--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="150">
   <si>
     <t>Id</t>
   </si>
@@ -71,6 +71,51 @@
     <t>string</t>
   </si>
   <si>
+    <t>神鉴·白</t>
+  </si>
+  <si>
+    <t>防御倍率</t>
+  </si>
+  <si>
+    <t>神鉴·绿</t>
+  </si>
+  <si>
+    <t>神鉴·蓝</t>
+  </si>
+  <si>
+    <t>神鉴·紫</t>
+  </si>
+  <si>
+    <t>神鉴·橙</t>
+  </si>
+  <si>
+    <t>神鉴·红</t>
+  </si>
+  <si>
+    <t>龙之怒</t>
+  </si>
+  <si>
+    <t>攻击倍率</t>
+  </si>
+  <si>
+    <t>龙之刀</t>
+  </si>
+  <si>
+    <t>物攻倍率</t>
+  </si>
+  <si>
+    <t>龙之杖</t>
+  </si>
+  <si>
+    <t>魔法倍率</t>
+  </si>
+  <si>
+    <t>龙之剑</t>
+  </si>
+  <si>
+    <t>道术倍率</t>
+  </si>
+  <si>
     <t>龙之血</t>
   </si>
   <si>
@@ -78,9 +123,6 @@
   </si>
   <si>
     <t>龙之御</t>
-  </si>
-  <si>
-    <t>防御倍率</t>
   </si>
   <si>
     <t>龙之力</t>
@@ -447,7 +489,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,6 +531,12 @@
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -981,16 +1029,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -999,120 +1044,124 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1122,6 +1171,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1441,7 +1491,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:Y123"/>
+  <dimension ref="A3:Y132"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1452,122 +1502,122 @@
   </cols>
   <sheetData>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="6" t="s">
+      <c r="D3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="N3" s="6" t="s">
+      <c r="M3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="6" t="s">
+      <c r="D4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="M4" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="N4" s="6" t="s">
+      <c r="M4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
+    <row r="6" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -1587,21 +1637,46 @@
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
     </row>
-    <row r="7" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
+    <row r="7" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="3">
+        <v>1999001</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2002</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1999001</v>
+      </c>
+      <c r="J7" s="3">
+        <v>7</v>
+      </c>
+      <c r="K7" s="3">
+        <v>10</v>
+      </c>
+      <c r="L7" s="3">
+        <v>1</v>
+      </c>
+      <c r="M7" s="3">
+        <v>1</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7" s="4"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
@@ -1609,21 +1684,46 @@
       <c r="U7" s="1"/>
       <c r="V7" s="1"/>
     </row>
-    <row r="8" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
+    <row r="8" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="3">
+        <v>1999002</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="3">
+        <v>2002</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1999002</v>
+      </c>
+      <c r="J8" s="3">
+        <v>7</v>
+      </c>
+      <c r="K8" s="3">
+        <v>10</v>
+      </c>
+      <c r="L8" s="3">
+        <v>1</v>
+      </c>
+      <c r="M8" s="3">
+        <v>1</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O8" s="4"/>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
@@ -1631,200 +1731,187 @@
       <c r="U8" s="1"/>
       <c r="V8" s="1"/>
     </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="2">
-        <v>1999993</v>
-      </c>
-      <c r="D9" s="2">
+    <row r="9" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="3">
+        <v>1999003</v>
+      </c>
+      <c r="D9" s="3">
         <v>0</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="2">
-        <v>2003</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2">
-        <v>1</v>
-      </c>
-      <c r="I9" s="2">
-        <v>1999993</v>
-      </c>
-      <c r="J9" s="2">
-        <v>6</v>
-      </c>
-      <c r="K9" s="2">
-        <v>10</v>
-      </c>
-      <c r="L9" s="2">
-        <v>1</v>
-      </c>
-      <c r="M9" s="2">
-        <v>1</v>
-      </c>
-      <c r="N9" s="2" t="s">
+      <c r="E9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="3">
+        <v>2002</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1999003</v>
+      </c>
+      <c r="J9" s="3">
+        <v>7</v>
+      </c>
+      <c r="K9" s="3">
+        <v>10</v>
+      </c>
+      <c r="L9" s="3">
+        <v>1</v>
+      </c>
+      <c r="M9" s="3">
+        <v>1</v>
+      </c>
+      <c r="N9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
+      <c r="O9" s="4"/>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-    </row>
-    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="2">
-        <v>1999994</v>
-      </c>
-      <c r="D10" s="2">
+    </row>
+    <row r="10" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="3">
+        <v>1999004</v>
+      </c>
+      <c r="D10" s="3">
         <v>0</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="2">
+      <c r="E10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="3">
         <v>2002</v>
       </c>
-      <c r="G10" s="2">
-        <v>1</v>
-      </c>
-      <c r="H10" s="2">
-        <v>1</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1999994</v>
-      </c>
-      <c r="J10" s="2">
-        <v>6</v>
-      </c>
-      <c r="K10" s="2">
-        <v>10</v>
-      </c>
-      <c r="L10" s="2">
-        <v>1</v>
-      </c>
-      <c r="M10" s="2">
-        <v>1</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1999004</v>
+      </c>
+      <c r="J10" s="3">
+        <v>7</v>
+      </c>
+      <c r="K10" s="3">
+        <v>10</v>
+      </c>
+      <c r="L10" s="3">
+        <v>1</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O10" s="4"/>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-    </row>
-    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="2">
-        <v>1999995</v>
-      </c>
-      <c r="D11" s="2">
+    </row>
+    <row r="11" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="3">
+        <v>1999005</v>
+      </c>
+      <c r="D11" s="3">
         <v>0</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="2">
-        <v>2007</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1999995</v>
-      </c>
-      <c r="J11" s="2">
-        <v>6</v>
-      </c>
-      <c r="K11" s="2">
-        <v>10</v>
-      </c>
-      <c r="L11" s="2">
-        <v>1</v>
-      </c>
-      <c r="M11" s="2">
-        <v>1</v>
-      </c>
-      <c r="N11" s="2" t="s">
+      <c r="E11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
+      <c r="F11" s="3">
+        <v>2002</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1999005</v>
+      </c>
+      <c r="J11" s="3">
+        <v>7</v>
+      </c>
+      <c r="K11" s="3">
+        <v>10</v>
+      </c>
+      <c r="L11" s="3">
+        <v>1</v>
+      </c>
+      <c r="M11" s="3">
+        <v>1</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O11" s="4"/>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-    </row>
-    <row r="12" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="2">
-        <v>1999996</v>
-      </c>
-      <c r="D12" s="2">
+    </row>
+    <row r="12" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="3">
+        <v>1999006</v>
+      </c>
+      <c r="D12" s="3">
         <v>0</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="2">
-        <v>2008</v>
-      </c>
-      <c r="G12" s="2">
-        <v>1</v>
-      </c>
-      <c r="H12" s="2">
-        <v>1</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1999996</v>
-      </c>
-      <c r="J12" s="2">
-        <v>6</v>
-      </c>
-      <c r="K12" s="2">
-        <v>10</v>
-      </c>
-      <c r="L12" s="2">
-        <v>1</v>
-      </c>
-      <c r="M12" s="2">
-        <v>1</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
+      <c r="F12" s="3">
+        <v>2002</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1999006</v>
+      </c>
+      <c r="J12" s="3">
+        <v>7</v>
+      </c>
+      <c r="K12" s="3">
+        <v>10</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1</v>
+      </c>
+      <c r="M12" s="3">
+        <v>1</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O12" s="4"/>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
@@ -1832,47 +1919,21 @@
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
     </row>
-    <row r="13" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="2">
-        <v>1999997</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="2">
-        <v>2009</v>
-      </c>
-      <c r="G13" s="2">
-        <v>1</v>
-      </c>
-      <c r="H13" s="2">
-        <v>1</v>
-      </c>
-      <c r="I13" s="2">
-        <v>1999997</v>
-      </c>
-      <c r="J13" s="2">
-        <v>6</v>
-      </c>
-      <c r="K13" s="2">
-        <v>10</v>
-      </c>
-      <c r="L13" s="2">
-        <v>1</v>
-      </c>
-      <c r="M13" s="2">
-        <v>1</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
+    <row r="13" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
       <c r="S13" s="1"/>
@@ -1880,43 +1941,46 @@
       <c r="U13" s="1"/>
       <c r="V13" s="1"/>
     </row>
-    <row r="14" s="3" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C14" s="2">
-        <v>1999998</v>
-      </c>
-      <c r="D14" s="2">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="3">
+        <v>1999989</v>
+      </c>
+      <c r="D14" s="3">
         <v>0</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F14" s="2">
-        <v>15</v>
-      </c>
-      <c r="G14" s="2">
-        <v>1</v>
-      </c>
-      <c r="H14" s="2">
-        <v>1</v>
-      </c>
-      <c r="I14" s="2">
-        <v>4101</v>
-      </c>
-      <c r="J14" s="2">
-        <v>5</v>
-      </c>
-      <c r="K14" s="2">
-        <v>200</v>
-      </c>
-      <c r="L14" s="2">
-        <v>10</v>
-      </c>
-      <c r="M14" s="2">
-        <v>20</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>25</v>
-      </c>
+      <c r="E14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="3">
+        <v>2001</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1999989</v>
+      </c>
+      <c r="J14" s="3">
+        <v>6</v>
+      </c>
+      <c r="K14" s="3">
+        <v>10</v>
+      </c>
+      <c r="L14" s="3">
+        <v>1</v>
+      </c>
+      <c r="M14" s="3">
+        <v>1</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O14" s="8"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
@@ -1924,43 +1988,46 @@
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
     </row>
-    <row r="15" s="3" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C15" s="2">
-        <v>1999999</v>
-      </c>
-      <c r="D15" s="2">
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="3">
+        <v>1999990</v>
+      </c>
+      <c r="D15" s="3">
         <v>0</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="2">
-        <v>14</v>
-      </c>
-      <c r="G15" s="2">
-        <v>1</v>
-      </c>
-      <c r="H15" s="2">
-        <v>1</v>
-      </c>
-      <c r="I15" s="2">
-        <v>4101</v>
-      </c>
-      <c r="J15" s="2">
-        <v>5</v>
-      </c>
-      <c r="K15" s="2">
-        <v>200</v>
-      </c>
-      <c r="L15" s="2">
-        <v>10</v>
-      </c>
-      <c r="M15" s="2">
-        <v>20</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="E15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F15" s="3">
+        <v>2004</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3">
+        <v>1999990</v>
+      </c>
+      <c r="J15" s="3">
+        <v>6</v>
+      </c>
+      <c r="K15" s="3">
+        <v>10</v>
+      </c>
+      <c r="L15" s="3">
+        <v>1</v>
+      </c>
+      <c r="M15" s="3">
+        <v>1</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O15" s="8"/>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
@@ -1968,42 +2035,44 @@
       <c r="U15" s="1"/>
       <c r="V15" s="1"/>
     </row>
-    <row r="16" s="3" customFormat="1" customHeight="1" spans="3:22">
-      <c r="C16" s="2">
-        <v>2000000</v>
-      </c>
-      <c r="D16" s="2">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="3">
+        <v>1999991</v>
+      </c>
+      <c r="D16" s="3">
         <v>0</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="2">
-        <v>16</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1</v>
-      </c>
-      <c r="H16" s="2">
-        <v>1</v>
-      </c>
-      <c r="I16" s="2">
-        <v>4101</v>
-      </c>
-      <c r="J16" s="2">
-        <v>5</v>
-      </c>
-      <c r="K16" s="2">
-        <v>200</v>
-      </c>
-      <c r="L16" s="2">
-        <v>10</v>
-      </c>
-      <c r="M16" s="2">
-        <v>20</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>29</v>
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>2005</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1</v>
+      </c>
+      <c r="I16" s="3">
+        <v>1999991</v>
+      </c>
+      <c r="J16" s="3">
+        <v>6</v>
+      </c>
+      <c r="K16" s="3">
+        <v>10</v>
+      </c>
+      <c r="L16" s="3">
+        <v>1</v>
+      </c>
+      <c r="M16" s="3">
+        <v>1</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
@@ -2012,531 +2081,528 @@
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
     </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="2">
-        <v>2000001</v>
-      </c>
-      <c r="D17" s="2">
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="3">
+        <v>1999992</v>
+      </c>
+      <c r="D17" s="3">
         <v>0</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="2">
-        <v>7</v>
-      </c>
-      <c r="G17" s="2">
-        <v>1</v>
-      </c>
-      <c r="H17" s="2">
-        <v>1</v>
-      </c>
-      <c r="I17" s="2">
-        <v>2000001</v>
-      </c>
-      <c r="J17" s="2">
-        <v>5</v>
-      </c>
-      <c r="K17" s="2">
-        <v>10</v>
-      </c>
-      <c r="L17" s="2">
-        <v>1</v>
-      </c>
-      <c r="M17" s="2">
-        <v>2</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
+      <c r="E17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="3">
+        <v>2006</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1999992</v>
+      </c>
+      <c r="J17" s="3">
+        <v>6</v>
+      </c>
+      <c r="K17" s="3">
+        <v>10</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1</v>
+      </c>
+      <c r="M17" s="3">
+        <v>1</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="2">
-        <v>2000002</v>
-      </c>
-      <c r="D18" s="2">
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="3">
+        <v>1999993</v>
+      </c>
+      <c r="D18" s="3">
         <v>0</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="2">
-        <v>14</v>
-      </c>
-      <c r="G18" s="2">
-        <v>5</v>
-      </c>
-      <c r="H18" s="2">
-        <v>5</v>
-      </c>
-      <c r="I18" s="2">
-        <v>2000002</v>
-      </c>
-      <c r="J18" s="2">
-        <v>5</v>
-      </c>
-      <c r="K18" s="2">
-        <v>10</v>
-      </c>
-      <c r="L18" s="2">
-        <v>1</v>
-      </c>
-      <c r="M18" s="2">
-        <v>2</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
+      <c r="E18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2003</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1999993</v>
+      </c>
+      <c r="J18" s="3">
+        <v>6</v>
+      </c>
+      <c r="K18" s="3">
+        <v>10</v>
+      </c>
+      <c r="L18" s="3">
+        <v>1</v>
+      </c>
+      <c r="M18" s="3">
+        <v>1</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O18" s="4"/>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="2">
-        <v>2000003</v>
-      </c>
-      <c r="D19" s="2">
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="3">
+        <v>1999994</v>
+      </c>
+      <c r="D19" s="3">
         <v>0</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="2">
-        <v>8</v>
-      </c>
-      <c r="G19" s="2">
-        <v>1</v>
-      </c>
-      <c r="H19" s="2">
-        <v>1</v>
-      </c>
-      <c r="I19" s="2">
-        <v>2000003</v>
-      </c>
-      <c r="J19" s="2">
-        <v>5</v>
-      </c>
-      <c r="K19" s="2">
-        <v>10</v>
-      </c>
-      <c r="L19" s="2">
-        <v>1</v>
-      </c>
-      <c r="M19" s="2">
-        <v>2</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
+      <c r="E19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2002</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1</v>
+      </c>
+      <c r="H19" s="3">
+        <v>1</v>
+      </c>
+      <c r="I19" s="3">
+        <v>1999994</v>
+      </c>
+      <c r="J19" s="3">
+        <v>6</v>
+      </c>
+      <c r="K19" s="3">
+        <v>10</v>
+      </c>
+      <c r="L19" s="3">
+        <v>1</v>
+      </c>
+      <c r="M19" s="3">
+        <v>1</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O19" s="4"/>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
       <c r="U19" s="1"/>
       <c r="V19" s="1"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="2">
-        <v>2000004</v>
-      </c>
-      <c r="D20" s="2">
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="3">
+        <v>1999995</v>
+      </c>
+      <c r="D20" s="3">
         <v>0</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F20" s="2">
-        <v>9</v>
-      </c>
-      <c r="G20" s="2">
-        <v>5</v>
-      </c>
-      <c r="H20" s="2">
-        <v>5</v>
-      </c>
-      <c r="I20" s="2">
-        <v>2000004</v>
-      </c>
-      <c r="J20" s="2">
-        <v>5</v>
-      </c>
-      <c r="K20" s="2">
-        <v>10</v>
-      </c>
-      <c r="L20" s="2">
-        <v>1</v>
-      </c>
-      <c r="M20" s="2">
-        <v>2</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
+      <c r="E20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="3">
+        <v>2007</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1999995</v>
+      </c>
+      <c r="J20" s="3">
+        <v>6</v>
+      </c>
+      <c r="K20" s="3">
+        <v>10</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1</v>
+      </c>
+      <c r="M20" s="3">
+        <v>1</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="O20" s="4"/>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="2">
-        <v>2000005</v>
-      </c>
-      <c r="D21" s="2">
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="3">
+        <v>1999996</v>
+      </c>
+      <c r="D21" s="3">
         <v>0</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F21" s="2">
-        <v>12</v>
-      </c>
-      <c r="G21" s="2">
-        <v>1</v>
-      </c>
-      <c r="H21" s="2">
-        <v>1</v>
-      </c>
-      <c r="I21" s="2">
-        <v>2000005</v>
-      </c>
-      <c r="J21" s="2">
-        <v>5</v>
-      </c>
-      <c r="K21" s="2">
-        <v>10</v>
-      </c>
-      <c r="L21" s="2">
-        <v>1</v>
-      </c>
-      <c r="M21" s="2">
-        <v>2</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
+      <c r="E21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F21" s="3">
+        <v>2008</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1999996</v>
+      </c>
+      <c r="J21" s="3">
+        <v>6</v>
+      </c>
+      <c r="K21" s="3">
+        <v>10</v>
+      </c>
+      <c r="L21" s="3">
+        <v>1</v>
+      </c>
+      <c r="M21" s="3">
+        <v>1</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O21" s="4"/>
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
       <c r="T21" s="1"/>
       <c r="U21" s="1"/>
       <c r="V21" s="1"/>
-      <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="2">
-        <v>2000006</v>
-      </c>
-      <c r="D22" s="2">
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="3">
+        <v>1999997</v>
+      </c>
+      <c r="D22" s="3">
         <v>0</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F22" s="2">
-        <v>14</v>
-      </c>
-      <c r="G22" s="2">
-        <v>5</v>
-      </c>
-      <c r="H22" s="2">
-        <v>5</v>
-      </c>
-      <c r="I22" s="2">
-        <v>2000006</v>
-      </c>
-      <c r="J22" s="2">
-        <v>5</v>
-      </c>
-      <c r="K22" s="2">
-        <v>10</v>
-      </c>
-      <c r="L22" s="2">
-        <v>1</v>
-      </c>
-      <c r="M22" s="2">
-        <v>1</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
+      <c r="E22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="3">
+        <v>2009</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1</v>
+      </c>
+      <c r="H22" s="3">
+        <v>1</v>
+      </c>
+      <c r="I22" s="3">
+        <v>1999997</v>
+      </c>
+      <c r="J22" s="3">
+        <v>6</v>
+      </c>
+      <c r="K22" s="3">
+        <v>10</v>
+      </c>
+      <c r="L22" s="3">
+        <v>1</v>
+      </c>
+      <c r="M22" s="3">
+        <v>1</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O22" s="4"/>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
       <c r="V22" s="1"/>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="2">
-        <v>2000007</v>
-      </c>
-      <c r="D23" s="2">
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="3">
+        <v>1999998</v>
+      </c>
+      <c r="D23" s="3">
         <v>0</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F23" s="2">
-        <v>16</v>
-      </c>
-      <c r="G23" s="2">
+        <v>38</v>
+      </c>
+      <c r="F23" s="3">
+        <v>15</v>
+      </c>
+      <c r="G23" s="3">
+        <v>1</v>
+      </c>
+      <c r="H23" s="3">
+        <v>1</v>
+      </c>
+      <c r="I23" s="3">
+        <v>4101</v>
+      </c>
+      <c r="J23" s="3">
         <v>5</v>
       </c>
-      <c r="H23" s="2">
-        <v>5</v>
-      </c>
-      <c r="I23" s="2">
-        <v>2000007</v>
-      </c>
-      <c r="J23" s="2">
-        <v>5</v>
-      </c>
-      <c r="K23" s="2">
-        <v>10</v>
-      </c>
-      <c r="L23" s="2">
-        <v>1</v>
-      </c>
-      <c r="M23" s="2">
-        <v>1</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O23" s="3"/>
-      <c r="P23" s="3"/>
+      <c r="K23" s="3">
+        <v>200</v>
+      </c>
+      <c r="L23" s="3">
+        <v>10</v>
+      </c>
+      <c r="M23" s="3">
+        <v>20</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O23" s="4"/>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
-      <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="2">
-        <v>2000008</v>
-      </c>
-      <c r="D24" s="2">
+    </row>
+    <row r="24" s="3" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="3">
+        <v>1999999</v>
+      </c>
+      <c r="D24" s="3">
         <v>0</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="3">
+        <v>14</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1</v>
+      </c>
+      <c r="H24" s="3">
+        <v>1</v>
+      </c>
+      <c r="I24" s="3">
+        <v>4101</v>
+      </c>
+      <c r="J24" s="3">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
+        <v>200</v>
+      </c>
+      <c r="L24" s="3">
+        <v>10</v>
+      </c>
+      <c r="M24" s="3">
+        <v>20</v>
+      </c>
+      <c r="N24" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="2">
-        <v>15</v>
-      </c>
-      <c r="G24" s="2">
-        <v>5</v>
-      </c>
-      <c r="H24" s="2">
-        <v>5</v>
-      </c>
-      <c r="I24" s="2">
-        <v>2000008</v>
-      </c>
-      <c r="J24" s="2">
-        <v>5</v>
-      </c>
-      <c r="K24" s="2">
-        <v>10</v>
-      </c>
-      <c r="L24" s="2">
-        <v>1</v>
-      </c>
-      <c r="M24" s="2">
-        <v>1</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="2">
-        <v>2000009</v>
-      </c>
-      <c r="D25" s="2">
+      <c r="W24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
+    </row>
+    <row r="25" s="3" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="3">
+        <v>2000000</v>
+      </c>
+      <c r="D25" s="3">
         <v>0</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F25" s="2">
-        <v>12</v>
-      </c>
-      <c r="G25" s="2">
-        <v>1</v>
-      </c>
-      <c r="H25" s="2">
-        <v>1</v>
-      </c>
-      <c r="I25" s="2">
-        <v>2000009</v>
-      </c>
-      <c r="J25" s="2">
+      <c r="F25" s="3">
+        <v>16</v>
+      </c>
+      <c r="G25" s="3">
+        <v>1</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3">
+        <v>4101</v>
+      </c>
+      <c r="J25" s="3">
         <v>5</v>
       </c>
-      <c r="K25" s="2">
-        <v>10</v>
-      </c>
-      <c r="L25" s="2">
-        <v>1</v>
-      </c>
-      <c r="M25" s="2">
-        <v>1</v>
-      </c>
-      <c r="N25" s="2" t="s">
+      <c r="K25" s="3">
+        <v>200</v>
+      </c>
+      <c r="L25" s="3">
+        <v>10</v>
+      </c>
+      <c r="M25" s="3">
+        <v>20</v>
+      </c>
+      <c r="N25" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="O25" s="3"/>
-      <c r="P25" s="3"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="2">
-        <v>2000010</v>
-      </c>
-      <c r="D26" s="2">
+      <c r="W25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+    </row>
+    <row r="26" s="3" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="3">
+        <v>2000001</v>
+      </c>
+      <c r="D26" s="3">
         <v>0</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F26" s="2">
-        <v>13</v>
-      </c>
-      <c r="G26" s="2">
-        <v>1</v>
-      </c>
-      <c r="H26" s="2">
-        <v>1</v>
-      </c>
-      <c r="I26" s="2">
-        <v>2000010</v>
-      </c>
-      <c r="J26" s="2">
+      <c r="F26" s="3">
+        <v>7</v>
+      </c>
+      <c r="G26" s="3">
+        <v>1</v>
+      </c>
+      <c r="H26" s="3">
+        <v>1</v>
+      </c>
+      <c r="I26" s="3">
+        <v>2000001</v>
+      </c>
+      <c r="J26" s="3">
         <v>5</v>
       </c>
-      <c r="K26" s="2">
-        <v>10</v>
-      </c>
-      <c r="L26" s="2">
-        <v>1</v>
-      </c>
-      <c r="M26" s="2">
-        <v>1</v>
-      </c>
-      <c r="N26" s="2" t="s">
+      <c r="K26" s="3">
+        <v>10</v>
+      </c>
+      <c r="L26" s="3">
+        <v>1</v>
+      </c>
+      <c r="M26" s="3">
+        <v>2</v>
+      </c>
+      <c r="N26" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
       <c r="U26" s="1"/>
       <c r="V26" s="1"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-    </row>
-    <row r="27" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
+      <c r="W26" s="4"/>
+      <c r="X26" s="4"/>
+      <c r="Y26" s="4"/>
+    </row>
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="3">
+        <v>2000002</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="3">
+        <v>14</v>
+      </c>
+      <c r="G27" s="3">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3">
+        <v>5</v>
+      </c>
+      <c r="I27" s="3">
+        <v>2000002</v>
+      </c>
+      <c r="J27" s="3">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3">
+        <v>10</v>
+      </c>
+      <c r="L27" s="3">
+        <v>1</v>
+      </c>
+      <c r="M27" s="3">
+        <v>2</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
@@ -2544,21 +2610,47 @@
       <c r="U27" s="1"/>
       <c r="V27" s="1"/>
     </row>
-    <row r="28" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="3">
+        <v>2000003</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28" s="3">
+        <v>8</v>
+      </c>
+      <c r="G28" s="3">
+        <v>1</v>
+      </c>
+      <c r="H28" s="3">
+        <v>1</v>
+      </c>
+      <c r="I28" s="3">
+        <v>2000003</v>
+      </c>
+      <c r="J28" s="3">
+        <v>5</v>
+      </c>
+      <c r="K28" s="3">
+        <v>10</v>
+      </c>
+      <c r="L28" s="3">
+        <v>1</v>
+      </c>
+      <c r="M28" s="3">
+        <v>2</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
@@ -2566,1540 +2658,1710 @@
       <c r="U28" s="1"/>
       <c r="V28" s="1"/>
     </row>
-    <row r="29" customFormat="1" customHeight="1" spans="1:21">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
+    <row r="29" s="4" customFormat="1" customHeight="1" spans="3:22">
+      <c r="C29" s="3">
+        <v>2000004</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F29" s="3">
+        <v>9</v>
+      </c>
+      <c r="G29" s="3">
+        <v>5</v>
+      </c>
+      <c r="H29" s="3">
+        <v>5</v>
+      </c>
+      <c r="I29" s="3">
+        <v>2000004</v>
+      </c>
+      <c r="J29" s="3">
+        <v>5</v>
+      </c>
+      <c r="K29" s="3">
+        <v>10</v>
+      </c>
+      <c r="L29" s="3">
+        <v>1</v>
+      </c>
+      <c r="M29" s="3">
+        <v>2</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="O29" s="4"/>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
       <c r="U29" s="1"/>
-    </row>
-    <row r="30" customFormat="1" customHeight="1" spans="3:21">
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
+      <c r="V29" s="1"/>
+    </row>
+    <row r="30" s="4" customFormat="1" customHeight="1" spans="3:22">
+      <c r="C30" s="3">
+        <v>2000005</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F30" s="3">
+        <v>12</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1</v>
+      </c>
+      <c r="H30" s="3">
+        <v>1</v>
+      </c>
+      <c r="I30" s="3">
+        <v>2000005</v>
+      </c>
+      <c r="J30" s="3">
+        <v>5</v>
+      </c>
+      <c r="K30" s="3">
+        <v>10</v>
+      </c>
+      <c r="L30" s="3">
+        <v>1</v>
+      </c>
+      <c r="M30" s="3">
+        <v>2</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="O30" s="4"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
       <c r="U30" s="1"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C31" s="1">
+      <c r="V30" s="1"/>
+    </row>
+    <row r="31" s="4" customFormat="1" customHeight="1" spans="3:22">
+      <c r="C31" s="3">
+        <v>2000006</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" s="3">
+        <v>14</v>
+      </c>
+      <c r="G31" s="3">
+        <v>5</v>
+      </c>
+      <c r="H31" s="3">
+        <v>5</v>
+      </c>
+      <c r="I31" s="3">
+        <v>2000006</v>
+      </c>
+      <c r="J31" s="3">
+        <v>5</v>
+      </c>
+      <c r="K31" s="3">
+        <v>10</v>
+      </c>
+      <c r="L31" s="3">
+        <v>1</v>
+      </c>
+      <c r="M31" s="3">
+        <v>1</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O31" s="4"/>
+      <c r="Q31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="S31" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
+    </row>
+    <row r="32" s="3" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="4"/>
+      <c r="C32" s="3">
+        <v>2000007</v>
+      </c>
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32" s="3">
+        <v>16</v>
+      </c>
+      <c r="G32" s="3">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2000007</v>
+      </c>
+      <c r="J32" s="3">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
+        <v>10</v>
+      </c>
+      <c r="L32" s="3">
+        <v>1</v>
+      </c>
+      <c r="M32" s="3">
+        <v>1</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="O32" s="4"/>
+      <c r="P32" s="4"/>
+      <c r="Q32" s="1"/>
+      <c r="R32" s="1"/>
+      <c r="S32" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="4"/>
+      <c r="X32" s="4"/>
+      <c r="Y32" s="4"/>
+    </row>
+    <row r="33" s="3" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
+      <c r="C33" s="3">
+        <v>2000008</v>
+      </c>
+      <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F33" s="3">
+        <v>15</v>
+      </c>
+      <c r="G33" s="3">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3">
+        <v>5</v>
+      </c>
+      <c r="I33" s="3">
+        <v>2000008</v>
+      </c>
+      <c r="J33" s="3">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3">
+        <v>10</v>
+      </c>
+      <c r="L33" s="3">
+        <v>1</v>
+      </c>
+      <c r="M33" s="3">
+        <v>1</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4"/>
+      <c r="Q33" s="1"/>
+      <c r="R33" s="1"/>
+      <c r="S33" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="1"/>
+      <c r="W33" s="4"/>
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4"/>
+    </row>
+    <row r="34" s="3" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="3">
+        <v>2000009</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F34" s="3">
+        <v>12</v>
+      </c>
+      <c r="G34" s="3">
+        <v>1</v>
+      </c>
+      <c r="H34" s="3">
+        <v>1</v>
+      </c>
+      <c r="I34" s="3">
+        <v>2000009</v>
+      </c>
+      <c r="J34" s="3">
+        <v>5</v>
+      </c>
+      <c r="K34" s="3">
+        <v>10</v>
+      </c>
+      <c r="L34" s="3">
+        <v>1</v>
+      </c>
+      <c r="M34" s="3">
+        <v>1</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="O34" s="4"/>
+      <c r="P34" s="4"/>
+      <c r="Q34" s="1"/>
+      <c r="R34" s="1"/>
+      <c r="S34" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="4"/>
+      <c r="X34" s="4"/>
+      <c r="Y34" s="4"/>
+    </row>
+    <row r="35" s="3" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="3">
+        <v>2000010</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F35" s="3">
+        <v>13</v>
+      </c>
+      <c r="G35" s="3">
+        <v>1</v>
+      </c>
+      <c r="H35" s="3">
+        <v>1</v>
+      </c>
+      <c r="I35" s="3">
+        <v>2000010</v>
+      </c>
+      <c r="J35" s="3">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3">
+        <v>10</v>
+      </c>
+      <c r="L35" s="3">
+        <v>1</v>
+      </c>
+      <c r="M35" s="3">
+        <v>1</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="O35" s="4"/>
+      <c r="P35" s="4"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+      <c r="U35" s="1"/>
+      <c r="V35" s="1"/>
+      <c r="W35" s="4"/>
+      <c r="X35" s="4"/>
+      <c r="Y35" s="4"/>
+    </row>
+    <row r="36" s="3" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="4"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+      <c r="U36" s="1"/>
+      <c r="V36" s="1"/>
+      <c r="W36" s="4"/>
+      <c r="X36" s="4"/>
+      <c r="Y36" s="4"/>
+    </row>
+    <row r="37" s="3" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="4"/>
+      <c r="Q37" s="1"/>
+      <c r="R37" s="1"/>
+      <c r="S37" s="1"/>
+      <c r="T37" s="1"/>
+      <c r="U37" s="1"/>
+      <c r="V37" s="1"/>
+      <c r="W37" s="4"/>
+      <c r="X37" s="4"/>
+      <c r="Y37" s="4"/>
+    </row>
+    <row r="38" s="3" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="4"/>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1"/>
+      <c r="S38" s="1"/>
+      <c r="T38" s="1"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="4"/>
+      <c r="X38" s="4"/>
+      <c r="Y38" s="4"/>
+    </row>
+    <row r="39" s="3" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="1"/>
+      <c r="R39" s="1"/>
+      <c r="S39" s="1"/>
+      <c r="T39" s="1"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="4"/>
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4"/>
+    </row>
+    <row r="40" s="3" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1">
         <v>2000100</v>
       </c>
-      <c r="D31" s="1">
-        <v>1</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="F31" s="1">
+      <c r="D40" s="1">
+        <v>1</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F40" s="1">
         <v>15</v>
       </c>
-      <c r="G31" s="1">
-        <v>1</v>
-      </c>
-      <c r="H31" s="1">
-        <v>1</v>
-      </c>
-      <c r="I31" s="1">
+      <c r="G40" s="1">
+        <v>1</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1</v>
+      </c>
+      <c r="I40" s="1">
         <v>2000100</v>
       </c>
-      <c r="J31" s="1">
-        <v>1</v>
-      </c>
-      <c r="K31" s="1">
-        <v>10</v>
-      </c>
-      <c r="L31" s="2">
-        <v>1</v>
-      </c>
-      <c r="M31" s="1">
-        <v>2</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C32" s="1">
+      <c r="J40" s="1">
+        <v>1</v>
+      </c>
+      <c r="K40" s="1">
+        <v>10</v>
+      </c>
+      <c r="L40" s="3">
+        <v>1</v>
+      </c>
+      <c r="M40" s="1">
+        <v>2</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O40" s="1"/>
+      <c r="P40" s="4"/>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="4"/>
+      <c r="X40" s="4"/>
+      <c r="Y40" s="4"/>
+    </row>
+    <row r="41" s="3" customFormat="1" customHeight="1" spans="1:25">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1">
         <v>2000101</v>
       </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F32" s="1">
+      <c r="D41" s="1">
+        <v>1</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F41" s="1">
         <v>15</v>
       </c>
-      <c r="G32" s="1">
-        <v>1</v>
-      </c>
-      <c r="H32" s="1">
-        <v>1</v>
-      </c>
-      <c r="I32" s="1">
+      <c r="G41" s="1">
+        <v>1</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1">
         <v>2000101</v>
       </c>
-      <c r="J32" s="1">
-        <v>1</v>
-      </c>
-      <c r="K32" s="1">
-        <v>10</v>
-      </c>
-      <c r="L32" s="2">
-        <v>1</v>
-      </c>
-      <c r="M32" s="1">
-        <v>2</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C33" s="1">
+      <c r="J41" s="1">
+        <v>1</v>
+      </c>
+      <c r="K41" s="1">
+        <v>10</v>
+      </c>
+      <c r="L41" s="3">
+        <v>1</v>
+      </c>
+      <c r="M41" s="1">
+        <v>2</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O41" s="1"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="1"/>
+      <c r="R41" s="1"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+    </row>
+    <row r="42" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1">
         <v>2000102</v>
       </c>
-      <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="F33" s="1">
+      <c r="D42" s="1">
+        <v>1</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F42" s="1">
         <v>15</v>
       </c>
-      <c r="G33" s="1">
-        <v>1</v>
-      </c>
-      <c r="H33" s="1">
-        <v>1</v>
-      </c>
-      <c r="I33" s="1">
+      <c r="G42" s="1">
+        <v>1</v>
+      </c>
+      <c r="H42" s="1">
+        <v>1</v>
+      </c>
+      <c r="I42" s="1">
         <v>2000102</v>
       </c>
-      <c r="J33" s="1">
-        <v>1</v>
-      </c>
-      <c r="K33" s="1">
-        <v>10</v>
-      </c>
-      <c r="L33" s="2">
-        <v>1</v>
-      </c>
-      <c r="M33" s="1">
-        <v>2</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C34" s="1">
+      <c r="J42" s="1">
+        <v>1</v>
+      </c>
+      <c r="K42" s="1">
+        <v>10</v>
+      </c>
+      <c r="L42" s="3">
+        <v>1</v>
+      </c>
+      <c r="M42" s="1">
+        <v>2</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O42" s="1"/>
+      <c r="Q42" s="1"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1"/>
+    </row>
+    <row r="43" s="2" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1">
         <v>2000103</v>
       </c>
-      <c r="D34" s="1">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F34" s="1">
+      <c r="D43" s="1">
+        <v>1</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F43" s="1">
         <v>15</v>
       </c>
-      <c r="G34" s="1">
-        <v>1</v>
-      </c>
-      <c r="H34" s="1">
-        <v>1</v>
-      </c>
-      <c r="I34" s="1">
+      <c r="G43" s="1">
+        <v>1</v>
+      </c>
+      <c r="H43" s="1">
+        <v>1</v>
+      </c>
+      <c r="I43" s="1">
         <v>2000103</v>
       </c>
-      <c r="J34" s="1">
-        <v>1</v>
-      </c>
-      <c r="K34" s="1">
-        <v>10</v>
-      </c>
-      <c r="L34" s="2">
-        <v>1</v>
-      </c>
-      <c r="M34" s="1">
-        <v>2</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C35" s="1">
+      <c r="J43" s="1">
+        <v>1</v>
+      </c>
+      <c r="K43" s="1">
+        <v>10</v>
+      </c>
+      <c r="L43" s="3">
+        <v>1</v>
+      </c>
+      <c r="M43" s="1">
+        <v>2</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O43" s="1"/>
+      <c r="Q43" s="1"/>
+      <c r="R43" s="1"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="1:21">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1">
         <v>2000104</v>
       </c>
-      <c r="D35" s="1">
-        <v>1</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F35" s="1">
+      <c r="D44" s="1">
+        <v>1</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F44" s="1">
         <v>14</v>
       </c>
-      <c r="G35" s="1">
-        <v>1</v>
-      </c>
-      <c r="H35" s="1">
-        <v>1</v>
-      </c>
-      <c r="I35" s="1">
+      <c r="G44" s="1">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1</v>
+      </c>
+      <c r="I44" s="1">
         <v>2000104</v>
       </c>
-      <c r="J35" s="1">
-        <v>1</v>
-      </c>
-      <c r="K35" s="1">
-        <v>10</v>
-      </c>
-      <c r="L35" s="2">
-        <v>1</v>
-      </c>
-      <c r="M35" s="1">
-        <v>2</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C36" s="1">
+      <c r="J44" s="1">
+        <v>1</v>
+      </c>
+      <c r="K44" s="1">
+        <v>10</v>
+      </c>
+      <c r="L44" s="3">
+        <v>1</v>
+      </c>
+      <c r="M44" s="1">
+        <v>2</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="1:21">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1">
         <v>2000105</v>
       </c>
-      <c r="D36" s="1">
-        <v>1</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F36" s="1">
+      <c r="D45" s="1">
+        <v>1</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F45" s="1">
         <v>14</v>
       </c>
-      <c r="G36" s="1">
-        <v>1</v>
-      </c>
-      <c r="H36" s="1">
-        <v>1</v>
-      </c>
-      <c r="I36" s="1">
+      <c r="G45" s="1">
+        <v>1</v>
+      </c>
+      <c r="H45" s="1">
+        <v>1</v>
+      </c>
+      <c r="I45" s="1">
         <v>2000105</v>
       </c>
-      <c r="J36" s="1">
-        <v>1</v>
-      </c>
-      <c r="K36" s="1">
-        <v>10</v>
-      </c>
-      <c r="L36" s="2">
-        <v>1</v>
-      </c>
-      <c r="M36" s="1">
-        <v>2</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C37" s="1">
+      <c r="J45" s="1">
+        <v>1</v>
+      </c>
+      <c r="K45" s="1">
+        <v>10</v>
+      </c>
+      <c r="L45" s="3">
+        <v>1</v>
+      </c>
+      <c r="M45" s="1">
+        <v>2</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C46" s="1">
         <v>2000106</v>
       </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F37" s="1">
+      <c r="D46" s="1">
+        <v>1</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F46" s="1">
         <v>14</v>
       </c>
-      <c r="G37" s="1">
-        <v>1</v>
-      </c>
-      <c r="H37" s="1">
-        <v>1</v>
-      </c>
-      <c r="I37" s="1">
+      <c r="G46" s="1">
+        <v>1</v>
+      </c>
+      <c r="H46" s="1">
+        <v>1</v>
+      </c>
+      <c r="I46" s="1">
         <v>2000106</v>
       </c>
-      <c r="J37" s="1">
-        <v>1</v>
-      </c>
-      <c r="K37" s="1">
-        <v>10</v>
-      </c>
-      <c r="L37" s="2">
-        <v>1</v>
-      </c>
-      <c r="M37" s="1">
-        <v>2</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C38" s="1">
+      <c r="J46" s="1">
+        <v>1</v>
+      </c>
+      <c r="K46" s="1">
+        <v>10</v>
+      </c>
+      <c r="L46" s="3">
+        <v>1</v>
+      </c>
+      <c r="M46" s="1">
+        <v>2</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C47" s="1">
         <v>2000107</v>
       </c>
-      <c r="D38" s="1">
-        <v>1</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F38" s="1">
+      <c r="D47" s="1">
+        <v>1</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F47" s="1">
         <v>14</v>
       </c>
-      <c r="G38" s="1">
-        <v>1</v>
-      </c>
-      <c r="H38" s="1">
-        <v>1</v>
-      </c>
-      <c r="I38" s="1">
+      <c r="G47" s="1">
+        <v>1</v>
+      </c>
+      <c r="H47" s="1">
+        <v>1</v>
+      </c>
+      <c r="I47" s="1">
         <v>2000107</v>
       </c>
-      <c r="J38" s="1">
-        <v>1</v>
-      </c>
-      <c r="K38" s="1">
-        <v>10</v>
-      </c>
-      <c r="L38" s="2">
-        <v>1</v>
-      </c>
-      <c r="M38" s="1">
-        <v>2</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:14">
-      <c r="C39" s="1">
+      <c r="J47" s="1">
+        <v>1</v>
+      </c>
+      <c r="K47" s="1">
+        <v>10</v>
+      </c>
+      <c r="L47" s="3">
+        <v>1</v>
+      </c>
+      <c r="M47" s="1">
+        <v>2</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C48" s="1">
         <v>2000108</v>
       </c>
-      <c r="D39" s="1">
-        <v>1</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F39" s="1">
+      <c r="D48" s="1">
+        <v>1</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F48" s="1">
         <v>16</v>
       </c>
-      <c r="G39" s="1">
-        <v>1</v>
-      </c>
-      <c r="H39" s="1">
-        <v>1</v>
-      </c>
-      <c r="I39" s="1">
+      <c r="G48" s="1">
+        <v>1</v>
+      </c>
+      <c r="H48" s="1">
+        <v>1</v>
+      </c>
+      <c r="I48" s="1">
         <v>2000108</v>
       </c>
-      <c r="J39" s="1">
-        <v>1</v>
-      </c>
-      <c r="K39" s="1">
-        <v>10</v>
-      </c>
-      <c r="L39" s="2">
-        <v>1</v>
-      </c>
-      <c r="M39" s="1">
-        <v>2</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:14">
-      <c r="C40" s="1">
+      <c r="J48" s="1">
+        <v>1</v>
+      </c>
+      <c r="K48" s="1">
+        <v>10</v>
+      </c>
+      <c r="L48" s="3">
+        <v>1</v>
+      </c>
+      <c r="M48" s="1">
+        <v>2</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C49" s="1">
         <v>2000109</v>
       </c>
-      <c r="D40" s="1">
-        <v>1</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F40" s="1">
+      <c r="D49" s="1">
+        <v>1</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F49" s="1">
         <v>16</v>
       </c>
-      <c r="G40" s="1">
-        <v>1</v>
-      </c>
-      <c r="H40" s="1">
-        <v>1</v>
-      </c>
-      <c r="I40" s="1">
+      <c r="G49" s="1">
+        <v>1</v>
+      </c>
+      <c r="H49" s="1">
+        <v>1</v>
+      </c>
+      <c r="I49" s="1">
         <v>2000109</v>
       </c>
-      <c r="J40" s="1">
-        <v>1</v>
-      </c>
-      <c r="K40" s="1">
-        <v>10</v>
-      </c>
-      <c r="L40" s="2">
-        <v>1</v>
-      </c>
-      <c r="M40" s="1">
-        <v>2</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:14">
-      <c r="C41" s="1">
+      <c r="J49" s="1">
+        <v>1</v>
+      </c>
+      <c r="K49" s="1">
+        <v>10</v>
+      </c>
+      <c r="L49" s="3">
+        <v>1</v>
+      </c>
+      <c r="M49" s="1">
+        <v>2</v>
+      </c>
+      <c r="N49" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C50" s="1">
         <v>2000110</v>
       </c>
-      <c r="D41" s="1">
-        <v>1</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F41" s="1">
+      <c r="D50" s="1">
+        <v>1</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F50" s="1">
         <v>16</v>
       </c>
-      <c r="G41" s="1">
-        <v>1</v>
-      </c>
-      <c r="H41" s="1">
-        <v>1</v>
-      </c>
-      <c r="I41" s="1">
+      <c r="G50" s="1">
+        <v>1</v>
+      </c>
+      <c r="H50" s="1">
+        <v>1</v>
+      </c>
+      <c r="I50" s="1">
         <v>2000110</v>
       </c>
-      <c r="J41" s="1">
-        <v>1</v>
-      </c>
-      <c r="K41" s="1">
-        <v>10</v>
-      </c>
-      <c r="L41" s="2">
-        <v>1</v>
-      </c>
-      <c r="M41" s="1">
-        <v>2</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:14">
-      <c r="C42" s="1">
+      <c r="J50" s="1">
+        <v>1</v>
+      </c>
+      <c r="K50" s="1">
+        <v>10</v>
+      </c>
+      <c r="L50" s="3">
+        <v>1</v>
+      </c>
+      <c r="M50" s="1">
+        <v>2</v>
+      </c>
+      <c r="N50" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:14">
+      <c r="C51" s="1">
         <v>2000111</v>
       </c>
-      <c r="D42" s="1">
-        <v>1</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="F42" s="1">
+      <c r="D51" s="1">
+        <v>1</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F51" s="1">
         <v>16</v>
       </c>
-      <c r="G42" s="1">
-        <v>1</v>
-      </c>
-      <c r="H42" s="1">
-        <v>1</v>
-      </c>
-      <c r="I42" s="1">
+      <c r="G51" s="1">
+        <v>1</v>
+      </c>
+      <c r="H51" s="1">
+        <v>1</v>
+      </c>
+      <c r="I51" s="1">
         <v>2000111</v>
       </c>
-      <c r="J42" s="1">
-        <v>1</v>
-      </c>
-      <c r="K42" s="1">
-        <v>10</v>
-      </c>
-      <c r="L42" s="2">
-        <v>1</v>
-      </c>
-      <c r="M42" s="1">
-        <v>2</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="43" s="4" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C43" s="1">
+      <c r="J51" s="1">
+        <v>1</v>
+      </c>
+      <c r="K51" s="1">
+        <v>10</v>
+      </c>
+      <c r="L51" s="3">
+        <v>1</v>
+      </c>
+      <c r="M51" s="1">
+        <v>2</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A52" s="5"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="1">
         <v>2000112</v>
       </c>
-      <c r="D43" s="1">
-        <v>1</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F43" s="4">
+      <c r="D52" s="1">
+        <v>1</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="F52" s="5">
         <v>15</v>
       </c>
-      <c r="G43" s="4">
-        <v>2</v>
-      </c>
-      <c r="H43" s="4">
-        <v>2</v>
-      </c>
-      <c r="I43" s="1">
+      <c r="G52" s="5">
+        <v>2</v>
+      </c>
+      <c r="H52" s="5">
+        <v>2</v>
+      </c>
+      <c r="I52" s="1">
         <v>2000112</v>
       </c>
-      <c r="J43" s="1">
-        <v>2</v>
-      </c>
-      <c r="K43" s="1">
-        <v>10</v>
-      </c>
-      <c r="L43" s="2">
-        <v>1</v>
-      </c>
-      <c r="M43" s="1">
-        <v>2</v>
-      </c>
-      <c r="N43" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="44" s="4" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C44" s="1">
+      <c r="J52" s="1">
+        <v>2</v>
+      </c>
+      <c r="K52" s="1">
+        <v>10</v>
+      </c>
+      <c r="L52" s="3">
+        <v>1</v>
+      </c>
+      <c r="M52" s="1">
+        <v>2</v>
+      </c>
+      <c r="N52" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="O52" s="5"/>
+    </row>
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A53" s="5"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="1">
         <v>2000113</v>
       </c>
-      <c r="D44" s="1">
-        <v>1</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F44" s="4">
+      <c r="D53" s="1">
+        <v>1</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F53" s="5">
         <v>15</v>
       </c>
-      <c r="G44" s="4">
-        <v>2</v>
-      </c>
-      <c r="H44" s="4">
-        <v>2</v>
-      </c>
-      <c r="I44" s="1">
+      <c r="G53" s="5">
+        <v>2</v>
+      </c>
+      <c r="H53" s="5">
+        <v>2</v>
+      </c>
+      <c r="I53" s="1">
         <v>2000113</v>
       </c>
-      <c r="J44" s="1">
-        <v>2</v>
-      </c>
-      <c r="K44" s="1">
-        <v>10</v>
-      </c>
-      <c r="L44" s="2">
-        <v>1</v>
-      </c>
-      <c r="M44" s="1">
-        <v>2</v>
-      </c>
-      <c r="N44" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="45" s="4" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C45" s="1">
+      <c r="J53" s="1">
+        <v>2</v>
+      </c>
+      <c r="K53" s="1">
+        <v>10</v>
+      </c>
+      <c r="L53" s="3">
+        <v>1</v>
+      </c>
+      <c r="M53" s="1">
+        <v>2</v>
+      </c>
+      <c r="N53" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="O53" s="5"/>
+    </row>
+    <row r="54" customHeight="1" spans="1:15">
+      <c r="A54" s="5"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="1">
         <v>2000114</v>
       </c>
-      <c r="D45" s="1">
-        <v>1</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F45" s="4">
+      <c r="D54" s="1">
+        <v>1</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F54" s="5">
         <v>15</v>
       </c>
-      <c r="G45" s="4">
-        <v>2</v>
-      </c>
-      <c r="H45" s="4">
-        <v>2</v>
-      </c>
-      <c r="I45" s="1">
+      <c r="G54" s="5">
+        <v>2</v>
+      </c>
+      <c r="H54" s="5">
+        <v>2</v>
+      </c>
+      <c r="I54" s="1">
         <v>2000114</v>
       </c>
-      <c r="J45" s="1">
-        <v>2</v>
-      </c>
-      <c r="K45" s="1">
-        <v>10</v>
-      </c>
-      <c r="L45" s="2">
-        <v>1</v>
-      </c>
-      <c r="M45" s="1">
-        <v>2</v>
-      </c>
-      <c r="N45" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="46" s="4" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C46" s="1">
+      <c r="J54" s="1">
+        <v>2</v>
+      </c>
+      <c r="K54" s="1">
+        <v>10</v>
+      </c>
+      <c r="L54" s="3">
+        <v>1</v>
+      </c>
+      <c r="M54" s="1">
+        <v>2</v>
+      </c>
+      <c r="N54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="O54" s="5"/>
+    </row>
+    <row r="55" customHeight="1" spans="1:15">
+      <c r="A55" s="5"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="1">
         <v>2000115</v>
       </c>
-      <c r="D46" s="1">
-        <v>1</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F46" s="4">
+      <c r="D55" s="1">
+        <v>1</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F55" s="5">
         <v>14</v>
       </c>
-      <c r="G46" s="4">
-        <v>2</v>
-      </c>
-      <c r="H46" s="4">
-        <v>2</v>
-      </c>
-      <c r="I46" s="1">
+      <c r="G55" s="5">
+        <v>2</v>
+      </c>
+      <c r="H55" s="5">
+        <v>2</v>
+      </c>
+      <c r="I55" s="1">
         <v>2000115</v>
       </c>
-      <c r="J46" s="1">
-        <v>2</v>
-      </c>
-      <c r="K46" s="1">
-        <v>10</v>
-      </c>
-      <c r="L46" s="2">
-        <v>1</v>
-      </c>
-      <c r="M46" s="1">
-        <v>2</v>
-      </c>
-      <c r="N46" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" s="4" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C47" s="1">
+      <c r="J55" s="1">
+        <v>2</v>
+      </c>
+      <c r="K55" s="1">
+        <v>10</v>
+      </c>
+      <c r="L55" s="3">
+        <v>1</v>
+      </c>
+      <c r="M55" s="1">
+        <v>2</v>
+      </c>
+      <c r="N55" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O55" s="5"/>
+    </row>
+    <row r="56" customHeight="1" spans="1:15">
+      <c r="A56" s="5"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="1">
         <v>2000116</v>
       </c>
-      <c r="D47" s="1">
-        <v>1</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F47" s="4">
+      <c r="D56" s="1">
+        <v>1</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F56" s="5">
         <v>14</v>
       </c>
-      <c r="G47" s="4">
-        <v>2</v>
-      </c>
-      <c r="H47" s="4">
-        <v>2</v>
-      </c>
-      <c r="I47" s="1">
+      <c r="G56" s="5">
+        <v>2</v>
+      </c>
+      <c r="H56" s="5">
+        <v>2</v>
+      </c>
+      <c r="I56" s="1">
         <v>2000116</v>
       </c>
-      <c r="J47" s="1">
-        <v>2</v>
-      </c>
-      <c r="K47" s="1">
-        <v>10</v>
-      </c>
-      <c r="L47" s="2">
-        <v>1</v>
-      </c>
-      <c r="M47" s="1">
-        <v>2</v>
-      </c>
-      <c r="N47" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" s="4" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C48" s="1">
+      <c r="J56" s="1">
+        <v>2</v>
+      </c>
+      <c r="K56" s="1">
+        <v>10</v>
+      </c>
+      <c r="L56" s="3">
+        <v>1</v>
+      </c>
+      <c r="M56" s="1">
+        <v>2</v>
+      </c>
+      <c r="N56" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O56" s="5"/>
+    </row>
+    <row r="57" customHeight="1" spans="1:15">
+      <c r="A57" s="5"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="1">
         <v>2000117</v>
       </c>
-      <c r="D48" s="1">
-        <v>1</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F48" s="4">
+      <c r="D57" s="1">
+        <v>1</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="F57" s="5">
         <v>14</v>
       </c>
-      <c r="G48" s="4">
-        <v>2</v>
-      </c>
-      <c r="H48" s="4">
-        <v>2</v>
-      </c>
-      <c r="I48" s="1">
+      <c r="G57" s="5">
+        <v>2</v>
+      </c>
+      <c r="H57" s="5">
+        <v>2</v>
+      </c>
+      <c r="I57" s="1">
         <v>2000117</v>
       </c>
-      <c r="J48" s="1">
-        <v>2</v>
-      </c>
-      <c r="K48" s="1">
-        <v>10</v>
-      </c>
-      <c r="L48" s="2">
-        <v>1</v>
-      </c>
-      <c r="M48" s="1">
-        <v>2</v>
-      </c>
-      <c r="N48" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" s="4" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C49" s="1">
-        <v>2000118</v>
-      </c>
-      <c r="D49" s="1">
-        <v>1</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F49" s="4">
-        <v>16</v>
-      </c>
-      <c r="G49" s="4">
-        <v>2</v>
-      </c>
-      <c r="H49" s="4">
-        <v>2</v>
-      </c>
-      <c r="I49" s="1">
-        <v>2000118</v>
-      </c>
-      <c r="J49" s="1">
-        <v>2</v>
-      </c>
-      <c r="K49" s="1">
-        <v>10</v>
-      </c>
-      <c r="L49" s="2">
-        <v>1</v>
-      </c>
-      <c r="M49" s="1">
-        <v>2</v>
-      </c>
-      <c r="N49" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="50" s="4" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C50" s="1">
-        <v>2000119</v>
-      </c>
-      <c r="D50" s="1">
-        <v>1</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F50" s="4">
-        <v>16</v>
-      </c>
-      <c r="G50" s="4">
-        <v>2</v>
-      </c>
-      <c r="H50" s="4">
-        <v>2</v>
-      </c>
-      <c r="I50" s="1">
-        <v>2000119</v>
-      </c>
-      <c r="J50" s="1">
-        <v>2</v>
-      </c>
-      <c r="K50" s="1">
-        <v>10</v>
-      </c>
-      <c r="L50" s="2">
-        <v>1</v>
-      </c>
-      <c r="M50" s="1">
-        <v>2</v>
-      </c>
-      <c r="N50" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="51" s="4" customFormat="1" customHeight="1" spans="3:14">
-      <c r="C51" s="1">
-        <v>2000120</v>
-      </c>
-      <c r="D51" s="1">
-        <v>1</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F51" s="4">
-        <v>16</v>
-      </c>
-      <c r="G51" s="4">
-        <v>2</v>
-      </c>
-      <c r="H51" s="4">
-        <v>2</v>
-      </c>
-      <c r="I51" s="1">
-        <v>2000120</v>
-      </c>
-      <c r="J51" s="1">
-        <v>2</v>
-      </c>
-      <c r="K51" s="1">
-        <v>10</v>
-      </c>
-      <c r="L51" s="2">
-        <v>1</v>
-      </c>
-      <c r="M51" s="1">
-        <v>2</v>
-      </c>
-      <c r="N51" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="52" customHeight="1" spans="3:14">
-      <c r="C52" s="1">
-        <v>2000121</v>
-      </c>
-      <c r="D52" s="1">
-        <v>1</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="F52" s="1">
-        <v>15</v>
-      </c>
-      <c r="G52" s="1">
-        <v>3</v>
-      </c>
-      <c r="H52" s="1">
-        <v>3</v>
-      </c>
-      <c r="I52" s="1">
-        <v>2000121</v>
-      </c>
-      <c r="J52" s="1">
-        <v>3</v>
-      </c>
-      <c r="K52" s="1">
-        <v>10</v>
-      </c>
-      <c r="L52" s="2">
-        <v>1</v>
-      </c>
-      <c r="M52" s="1">
-        <v>2</v>
-      </c>
-      <c r="N52" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:14">
-      <c r="C53" s="1">
-        <v>2000122</v>
-      </c>
-      <c r="D53" s="1">
-        <v>1</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F53" s="1">
-        <v>15</v>
-      </c>
-      <c r="G53" s="1">
-        <v>3</v>
-      </c>
-      <c r="H53" s="1">
-        <v>3</v>
-      </c>
-      <c r="I53" s="1">
-        <v>2000122</v>
-      </c>
-      <c r="J53" s="1">
-        <v>3</v>
-      </c>
-      <c r="K53" s="1">
-        <v>10</v>
-      </c>
-      <c r="L53" s="2">
-        <v>1</v>
-      </c>
-      <c r="M53" s="1">
-        <v>2</v>
-      </c>
-      <c r="N53" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="54" customHeight="1" spans="3:14">
-      <c r="C54" s="1">
-        <v>2000123</v>
-      </c>
-      <c r="D54" s="1">
-        <v>1</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F54" s="1">
-        <v>14</v>
-      </c>
-      <c r="G54" s="1">
-        <v>3</v>
-      </c>
-      <c r="H54" s="1">
-        <v>3</v>
-      </c>
-      <c r="I54" s="1">
-        <v>2000123</v>
-      </c>
-      <c r="J54" s="1">
-        <v>3</v>
-      </c>
-      <c r="K54" s="1">
-        <v>10</v>
-      </c>
-      <c r="L54" s="2">
-        <v>1</v>
-      </c>
-      <c r="M54" s="1">
-        <v>2</v>
-      </c>
-      <c r="N54" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="55" customHeight="1" spans="3:14">
-      <c r="C55" s="1">
-        <v>2000124</v>
-      </c>
-      <c r="D55" s="1">
-        <v>1</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F55" s="1">
-        <v>14</v>
-      </c>
-      <c r="G55" s="1">
-        <v>3</v>
-      </c>
-      <c r="H55" s="1">
-        <v>3</v>
-      </c>
-      <c r="I55" s="1">
-        <v>2000124</v>
-      </c>
-      <c r="J55" s="1">
-        <v>3</v>
-      </c>
-      <c r="K55" s="1">
-        <v>10</v>
-      </c>
-      <c r="L55" s="2">
-        <v>1</v>
-      </c>
-      <c r="M55" s="1">
-        <v>2</v>
-      </c>
-      <c r="N55" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="56" customHeight="1" spans="3:14">
-      <c r="C56" s="1">
-        <v>2000125</v>
-      </c>
-      <c r="D56" s="1">
-        <v>1</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="F56" s="1">
-        <v>16</v>
-      </c>
-      <c r="G56" s="1">
-        <v>3</v>
-      </c>
-      <c r="H56" s="1">
-        <v>3</v>
-      </c>
-      <c r="I56" s="1">
-        <v>2000125</v>
-      </c>
-      <c r="J56" s="1">
-        <v>3</v>
-      </c>
-      <c r="K56" s="1">
-        <v>10</v>
-      </c>
-      <c r="L56" s="2">
-        <v>1</v>
-      </c>
-      <c r="M56" s="1">
-        <v>2</v>
-      </c>
-      <c r="N56" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="57" customHeight="1" spans="3:14">
-      <c r="C57" s="1">
-        <v>2000126</v>
-      </c>
-      <c r="D57" s="1">
-        <v>1</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F57" s="1">
-        <v>16</v>
-      </c>
-      <c r="G57" s="1">
-        <v>3</v>
-      </c>
-      <c r="H57" s="1">
-        <v>3</v>
-      </c>
-      <c r="I57" s="1">
-        <v>2000126</v>
-      </c>
       <c r="J57" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K57" s="1">
         <v>10</v>
       </c>
-      <c r="L57" s="2">
+      <c r="L57" s="3">
         <v>1</v>
       </c>
       <c r="M57" s="1">
         <v>2</v>
       </c>
-      <c r="N57" s="7" t="s">
-        <v>29</v>
-      </c>
+      <c r="N57" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="O57" s="5"/>
     </row>
     <row r="58" s="5" customFormat="1" customHeight="1" spans="3:14">
       <c r="C58" s="1">
-        <v>2000127</v>
+        <v>2000118</v>
       </c>
       <c r="D58" s="1">
         <v>1</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F58" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G58" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H58" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I58" s="1">
-        <v>2000127</v>
+        <v>2000118</v>
       </c>
       <c r="J58" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K58" s="1">
         <v>10</v>
       </c>
-      <c r="L58" s="2">
+      <c r="L58" s="3">
         <v>1</v>
       </c>
       <c r="M58" s="1">
         <v>2</v>
       </c>
       <c r="N58" s="5" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="59" s="5" customFormat="1" customHeight="1" spans="3:14">
       <c r="C59" s="1">
-        <v>2000128</v>
+        <v>2000119</v>
       </c>
       <c r="D59" s="1">
         <v>1</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F59" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G59" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H59" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I59" s="1">
-        <v>2000128</v>
+        <v>2000119</v>
       </c>
       <c r="J59" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K59" s="1">
         <v>10</v>
       </c>
-      <c r="L59" s="2">
+      <c r="L59" s="3">
         <v>1</v>
       </c>
       <c r="M59" s="1">
         <v>2</v>
       </c>
       <c r="N59" s="5" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" s="5" customFormat="1" customHeight="1" spans="3:14">
       <c r="C60" s="1">
-        <v>2000129</v>
+        <v>2000120</v>
       </c>
       <c r="D60" s="1">
         <v>1</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="F60" s="5">
         <v>16</v>
       </c>
       <c r="G60" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H60" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I60" s="1">
-        <v>2000129</v>
+        <v>2000120</v>
       </c>
       <c r="J60" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K60" s="1">
         <v>10</v>
       </c>
-      <c r="L60" s="2">
+      <c r="L60" s="3">
         <v>1</v>
       </c>
       <c r="M60" s="1">
         <v>2</v>
       </c>
       <c r="N60" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="62" customHeight="1" spans="3:14">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="61" s="5" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1">
+        <v>2000121</v>
+      </c>
+      <c r="D61" s="1">
+        <v>1</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F61" s="1">
+        <v>15</v>
+      </c>
+      <c r="G61" s="1">
+        <v>3</v>
+      </c>
+      <c r="H61" s="1">
+        <v>3</v>
+      </c>
+      <c r="I61" s="1">
+        <v>2000121</v>
+      </c>
+      <c r="J61" s="1">
+        <v>3</v>
+      </c>
+      <c r="K61" s="1">
+        <v>10</v>
+      </c>
+      <c r="L61" s="3">
+        <v>1</v>
+      </c>
+      <c r="M61" s="1">
+        <v>2</v>
+      </c>
+      <c r="N61" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="O61" s="1"/>
+    </row>
+    <row r="62" s="5" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
       <c r="C62" s="1">
-        <v>2000200</v>
+        <v>2000122</v>
       </c>
       <c r="D62" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="F62" s="1">
         <v>15</v>
       </c>
       <c r="G62" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H62" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I62" s="1">
-        <v>2000200</v>
+        <v>2000122</v>
       </c>
       <c r="J62" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K62" s="1">
         <v>10</v>
       </c>
-      <c r="L62" s="2">
+      <c r="L62" s="3">
         <v>1</v>
       </c>
       <c r="M62" s="1">
         <v>2</v>
       </c>
-      <c r="N62" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="63" customHeight="1" spans="3:14">
+      <c r="N62" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="O62" s="1"/>
+    </row>
+    <row r="63" s="5" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
       <c r="C63" s="1">
-        <v>2000201</v>
+        <v>2000123</v>
       </c>
       <c r="D63" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F63" s="1">
+        <v>14</v>
+      </c>
+      <c r="G63" s="1">
+        <v>3</v>
+      </c>
+      <c r="H63" s="1">
+        <v>3</v>
+      </c>
+      <c r="I63" s="1">
+        <v>2000123</v>
+      </c>
+      <c r="J63" s="1">
+        <v>3</v>
+      </c>
+      <c r="K63" s="1">
+        <v>10</v>
+      </c>
+      <c r="L63" s="3">
+        <v>1</v>
+      </c>
+      <c r="M63" s="1">
+        <v>2</v>
+      </c>
+      <c r="N63" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="O63" s="1"/>
+    </row>
+    <row r="64" s="5" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1">
+        <v>2000124</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F64" s="1">
+        <v>14</v>
+      </c>
+      <c r="G64" s="1">
+        <v>3</v>
+      </c>
+      <c r="H64" s="1">
+        <v>3</v>
+      </c>
+      <c r="I64" s="1">
+        <v>2000124</v>
+      </c>
+      <c r="J64" s="1">
+        <v>3</v>
+      </c>
+      <c r="K64" s="1">
+        <v>10</v>
+      </c>
+      <c r="L64" s="3">
+        <v>1</v>
+      </c>
+      <c r="M64" s="1">
+        <v>2</v>
+      </c>
+      <c r="N64" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="O64" s="1"/>
+    </row>
+    <row r="65" s="5" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1">
+        <v>2000125</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F65" s="1">
+        <v>16</v>
+      </c>
+      <c r="G65" s="1">
+        <v>3</v>
+      </c>
+      <c r="H65" s="1">
+        <v>3</v>
+      </c>
+      <c r="I65" s="1">
+        <v>2000125</v>
+      </c>
+      <c r="J65" s="1">
+        <v>3</v>
+      </c>
+      <c r="K65" s="1">
+        <v>10</v>
+      </c>
+      <c r="L65" s="3">
+        <v>1</v>
+      </c>
+      <c r="M65" s="1">
+        <v>2</v>
+      </c>
+      <c r="N65" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O65" s="1"/>
+    </row>
+    <row r="66" s="5" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1">
+        <v>2000126</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F66" s="1">
+        <v>16</v>
+      </c>
+      <c r="G66" s="1">
+        <v>3</v>
+      </c>
+      <c r="H66" s="1">
+        <v>3</v>
+      </c>
+      <c r="I66" s="1">
+        <v>2000126</v>
+      </c>
+      <c r="J66" s="1">
+        <v>3</v>
+      </c>
+      <c r="K66" s="1">
+        <v>10</v>
+      </c>
+      <c r="L66" s="3">
+        <v>1</v>
+      </c>
+      <c r="M66" s="1">
+        <v>2</v>
+      </c>
+      <c r="N66" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="O66" s="1"/>
+    </row>
+    <row r="67" customHeight="1" spans="1:15">
+      <c r="A67" s="6"/>
+      <c r="B67" s="6"/>
+      <c r="C67" s="1">
+        <v>2000127</v>
+      </c>
+      <c r="D67" s="1">
+        <v>1</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F67" s="6">
         <v>15</v>
       </c>
-      <c r="G63" s="1">
-        <v>1</v>
-      </c>
-      <c r="H63" s="1">
-        <v>1</v>
-      </c>
-      <c r="I63" s="1">
-        <v>2000201</v>
-      </c>
-      <c r="J63" s="1">
-        <v>1</v>
-      </c>
-      <c r="K63" s="1">
-        <v>10</v>
-      </c>
-      <c r="L63" s="2">
-        <v>1</v>
-      </c>
-      <c r="M63" s="1">
-        <v>2</v>
-      </c>
-      <c r="N63" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="64" customHeight="1" spans="3:14">
-      <c r="C64" s="1">
-        <v>2000202</v>
-      </c>
-      <c r="D64" s="1">
-        <v>2</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F64" s="1">
-        <v>15</v>
-      </c>
-      <c r="G64" s="1">
-        <v>1</v>
-      </c>
-      <c r="H64" s="1">
-        <v>1</v>
-      </c>
-      <c r="I64" s="1">
-        <v>2000202</v>
-      </c>
-      <c r="J64" s="1">
-        <v>1</v>
-      </c>
-      <c r="K64" s="1">
-        <v>10</v>
-      </c>
-      <c r="L64" s="2">
-        <v>1</v>
-      </c>
-      <c r="M64" s="1">
-        <v>2</v>
-      </c>
-      <c r="N64" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="65" customHeight="1" spans="3:14">
-      <c r="C65" s="1">
-        <v>2000203</v>
-      </c>
-      <c r="D65" s="1">
-        <v>2</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F65" s="1">
-        <v>15</v>
-      </c>
-      <c r="G65" s="1">
-        <v>1</v>
-      </c>
-      <c r="H65" s="1">
-        <v>1</v>
-      </c>
-      <c r="I65" s="1">
-        <v>2000203</v>
-      </c>
-      <c r="J65" s="1">
-        <v>1</v>
-      </c>
-      <c r="K65" s="1">
-        <v>10</v>
-      </c>
-      <c r="L65" s="2">
-        <v>1</v>
-      </c>
-      <c r="M65" s="1">
-        <v>2</v>
-      </c>
-      <c r="N65" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="66" customHeight="1" spans="3:14">
-      <c r="C66" s="1">
-        <v>2000204</v>
-      </c>
-      <c r="D66" s="1">
-        <v>2</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F66" s="1">
-        <v>15</v>
-      </c>
-      <c r="G66" s="1">
-        <v>1</v>
-      </c>
-      <c r="H66" s="1">
-        <v>1</v>
-      </c>
-      <c r="I66" s="1">
-        <v>2000204</v>
-      </c>
-      <c r="J66" s="1">
-        <v>1</v>
-      </c>
-      <c r="K66" s="1">
-        <v>10</v>
-      </c>
-      <c r="L66" s="2">
-        <v>1</v>
-      </c>
-      <c r="M66" s="1">
-        <v>2</v>
-      </c>
-      <c r="N66" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="67" customHeight="1" spans="3:14">
-      <c r="C67" s="1">
-        <v>2000205</v>
-      </c>
-      <c r="D67" s="1">
-        <v>2</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="F67" s="1">
-        <v>15</v>
-      </c>
-      <c r="G67" s="1">
-        <v>1</v>
-      </c>
-      <c r="H67" s="1">
-        <v>1</v>
+      <c r="G67" s="6">
+        <v>4</v>
+      </c>
+      <c r="H67" s="6">
+        <v>4</v>
       </c>
       <c r="I67" s="1">
-        <v>2000205</v>
+        <v>2000127</v>
       </c>
       <c r="J67" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K67" s="1">
         <v>10</v>
       </c>
-      <c r="L67" s="2">
+      <c r="L67" s="3">
         <v>1</v>
       </c>
       <c r="M67" s="1">
         <v>2</v>
       </c>
-      <c r="N67" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="68" customHeight="1" spans="3:14">
+      <c r="N67" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="O67" s="6"/>
+    </row>
+    <row r="68" customHeight="1" spans="1:15">
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
       <c r="C68" s="1">
-        <v>2000206</v>
+        <v>2000128</v>
       </c>
       <c r="D68" s="1">
-        <v>2</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="F68" s="1">
-        <v>15</v>
-      </c>
-      <c r="G68" s="1">
-        <v>1</v>
-      </c>
-      <c r="H68" s="1">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F68" s="6">
+        <v>14</v>
+      </c>
+      <c r="G68" s="6">
+        <v>4</v>
+      </c>
+      <c r="H68" s="6">
+        <v>4</v>
       </c>
       <c r="I68" s="1">
-        <v>2000206</v>
+        <v>2000128</v>
       </c>
       <c r="J68" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K68" s="1">
         <v>10</v>
       </c>
-      <c r="L68" s="2">
+      <c r="L68" s="3">
         <v>1</v>
       </c>
       <c r="M68" s="1">
         <v>2</v>
       </c>
-      <c r="N68" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="69" customHeight="1" spans="3:14">
+      <c r="N68" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="O68" s="6"/>
+    </row>
+    <row r="69" customHeight="1" spans="1:15">
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
       <c r="C69" s="1">
-        <v>2000207</v>
+        <v>2000129</v>
       </c>
       <c r="D69" s="1">
-        <v>2</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="F69" s="1">
+        <v>1</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F69" s="6">
         <v>16</v>
       </c>
-      <c r="G69" s="1">
-        <v>1</v>
-      </c>
-      <c r="H69" s="1">
-        <v>1</v>
+      <c r="G69" s="6">
+        <v>4</v>
+      </c>
+      <c r="H69" s="6">
+        <v>4</v>
       </c>
       <c r="I69" s="1">
-        <v>2000207</v>
+        <v>2000129</v>
       </c>
       <c r="J69" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K69" s="1">
         <v>10</v>
       </c>
-      <c r="L69" s="2">
+      <c r="L69" s="3">
         <v>1</v>
       </c>
       <c r="M69" s="1">
         <v>2</v>
       </c>
-      <c r="N69" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="70" customHeight="1" spans="3:14">
-      <c r="C70" s="1">
-        <v>2000208</v>
-      </c>
-      <c r="D70" s="1">
-        <v>2</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F70" s="1">
-        <v>16</v>
-      </c>
-      <c r="G70" s="1">
-        <v>1</v>
-      </c>
-      <c r="H70" s="1">
-        <v>1</v>
-      </c>
-      <c r="I70" s="1">
-        <v>2000208</v>
-      </c>
-      <c r="J70" s="1">
-        <v>1</v>
-      </c>
-      <c r="K70" s="1">
-        <v>10</v>
-      </c>
-      <c r="L70" s="2">
-        <v>1</v>
-      </c>
-      <c r="M70" s="1">
-        <v>2</v>
-      </c>
-      <c r="N70" s="1" t="s">
-        <v>29</v>
-      </c>
+      <c r="N69" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="O69" s="6"/>
     </row>
     <row r="71" customHeight="1" spans="3:14">
       <c r="C71" s="1">
-        <v>2000209</v>
+        <v>2000200</v>
       </c>
       <c r="D71" s="1">
         <v>2</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="F71" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G71" s="1">
         <v>1</v>
@@ -4108,7 +4370,7 @@
         <v>1</v>
       </c>
       <c r="I71" s="1">
-        <v>2000209</v>
+        <v>2000200</v>
       </c>
       <c r="J71" s="1">
         <v>1</v>
@@ -4116,28 +4378,28 @@
       <c r="K71" s="1">
         <v>10</v>
       </c>
-      <c r="L71" s="2">
+      <c r="L71" s="3">
         <v>1</v>
       </c>
       <c r="M71" s="1">
         <v>2</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="72" customHeight="1" spans="3:14">
       <c r="C72" s="1">
-        <v>2000210</v>
+        <v>2000201</v>
       </c>
       <c r="D72" s="1">
         <v>2</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F72" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G72" s="1">
         <v>1</v>
@@ -4146,7 +4408,7 @@
         <v>1</v>
       </c>
       <c r="I72" s="1">
-        <v>2000210</v>
+        <v>2000201</v>
       </c>
       <c r="J72" s="1">
         <v>1</v>
@@ -4154,28 +4416,30 @@
       <c r="K72" s="1">
         <v>10</v>
       </c>
-      <c r="L72" s="2">
+      <c r="L72" s="3">
         <v>1</v>
       </c>
       <c r="M72" s="1">
         <v>2</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="73" customHeight="1" spans="3:14">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="73" s="6" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
       <c r="C73" s="1">
-        <v>2000211</v>
+        <v>2000202</v>
       </c>
       <c r="D73" s="1">
         <v>2</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F73" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G73" s="1">
         <v>1</v>
@@ -4184,7 +4448,7 @@
         <v>1</v>
       </c>
       <c r="I73" s="1">
-        <v>2000211</v>
+        <v>2000202</v>
       </c>
       <c r="J73" s="1">
         <v>1</v>
@@ -4192,1054 +4456,1061 @@
       <c r="K73" s="1">
         <v>10</v>
       </c>
-      <c r="L73" s="2">
+      <c r="L73" s="3">
         <v>1</v>
       </c>
       <c r="M73" s="1">
         <v>2</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="74" customHeight="1" spans="3:14">
+        <v>39</v>
+      </c>
+      <c r="O73" s="1"/>
+    </row>
+    <row r="74" s="6" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
       <c r="C74" s="1">
-        <v>2000212</v>
+        <v>2000203</v>
       </c>
       <c r="D74" s="1">
         <v>2</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F74" s="4">
+        <v>93</v>
+      </c>
+      <c r="F74" s="1">
         <v>15</v>
       </c>
-      <c r="G74" s="4">
-        <v>2</v>
-      </c>
-      <c r="H74" s="4">
-        <v>2</v>
+      <c r="G74" s="1">
+        <v>1</v>
+      </c>
+      <c r="H74" s="1">
+        <v>1</v>
       </c>
       <c r="I74" s="1">
-        <v>2000212</v>
+        <v>2000203</v>
       </c>
       <c r="J74" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K74" s="1">
         <v>10</v>
       </c>
-      <c r="L74" s="2">
+      <c r="L74" s="3">
         <v>1</v>
       </c>
       <c r="M74" s="1">
         <v>2</v>
       </c>
-      <c r="N74" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="75" customHeight="1" spans="3:14">
+      <c r="N74" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O74" s="1"/>
+    </row>
+    <row r="75" s="6" customFormat="1" customHeight="1" spans="1:15">
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
       <c r="C75" s="1">
-        <v>2000213</v>
+        <v>2000204</v>
       </c>
       <c r="D75" s="1">
         <v>2</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="F75" s="4">
+        <v>94</v>
+      </c>
+      <c r="F75" s="1">
         <v>15</v>
       </c>
-      <c r="G75" s="4">
-        <v>2</v>
-      </c>
-      <c r="H75" s="4">
-        <v>2</v>
+      <c r="G75" s="1">
+        <v>1</v>
+      </c>
+      <c r="H75" s="1">
+        <v>1</v>
       </c>
       <c r="I75" s="1">
-        <v>2000213</v>
+        <v>2000204</v>
       </c>
       <c r="J75" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K75" s="1">
         <v>10</v>
       </c>
-      <c r="L75" s="2">
+      <c r="L75" s="3">
         <v>1</v>
       </c>
       <c r="M75" s="1">
         <v>2</v>
       </c>
-      <c r="N75" s="4" t="s">
-        <v>25</v>
-      </c>
+      <c r="N75" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O75" s="1"/>
     </row>
     <row r="76" customHeight="1" spans="3:14">
       <c r="C76" s="1">
-        <v>2000214</v>
+        <v>2000205</v>
       </c>
       <c r="D76" s="1">
         <v>2</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="F76" s="4">
+        <v>95</v>
+      </c>
+      <c r="F76" s="1">
         <v>15</v>
       </c>
-      <c r="G76" s="4">
-        <v>2</v>
-      </c>
-      <c r="H76" s="4">
-        <v>2</v>
+      <c r="G76" s="1">
+        <v>1</v>
+      </c>
+      <c r="H76" s="1">
+        <v>1</v>
       </c>
       <c r="I76" s="1">
-        <v>2000214</v>
+        <v>2000205</v>
       </c>
       <c r="J76" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K76" s="1">
         <v>10</v>
       </c>
-      <c r="L76" s="2">
+      <c r="L76" s="3">
         <v>1</v>
       </c>
       <c r="M76" s="1">
         <v>2</v>
       </c>
-      <c r="N76" s="4" t="s">
-        <v>25</v>
+      <c r="N76" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="77" customHeight="1" spans="3:14">
       <c r="C77" s="1">
-        <v>2000215</v>
+        <v>2000206</v>
       </c>
       <c r="D77" s="1">
         <v>2</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F77" s="4">
+        <v>96</v>
+      </c>
+      <c r="F77" s="1">
         <v>15</v>
       </c>
-      <c r="G77" s="4">
-        <v>2</v>
-      </c>
-      <c r="H77" s="4">
-        <v>2</v>
+      <c r="G77" s="1">
+        <v>1</v>
+      </c>
+      <c r="H77" s="1">
+        <v>1</v>
       </c>
       <c r="I77" s="1">
-        <v>2000215</v>
+        <v>2000206</v>
       </c>
       <c r="J77" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K77" s="1">
         <v>10</v>
       </c>
-      <c r="L77" s="2">
+      <c r="L77" s="3">
         <v>1</v>
       </c>
       <c r="M77" s="1">
         <v>2</v>
       </c>
-      <c r="N77" s="4" t="s">
-        <v>25</v>
+      <c r="N77" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="78" customHeight="1" spans="3:14">
       <c r="C78" s="1">
-        <v>2000216</v>
+        <v>2000207</v>
       </c>
       <c r="D78" s="1">
         <v>2</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="F78" s="4">
-        <v>15</v>
-      </c>
-      <c r="G78" s="4">
-        <v>2</v>
-      </c>
-      <c r="H78" s="4">
-        <v>2</v>
+        <v>97</v>
+      </c>
+      <c r="F78" s="1">
+        <v>16</v>
+      </c>
+      <c r="G78" s="1">
+        <v>1</v>
+      </c>
+      <c r="H78" s="1">
+        <v>1</v>
       </c>
       <c r="I78" s="1">
-        <v>2000216</v>
+        <v>2000207</v>
       </c>
       <c r="J78" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K78" s="1">
         <v>10</v>
       </c>
-      <c r="L78" s="2">
+      <c r="L78" s="3">
         <v>1</v>
       </c>
       <c r="M78" s="1">
         <v>2</v>
       </c>
-      <c r="N78" s="4" t="s">
-        <v>25</v>
+      <c r="N78" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="79" customHeight="1" spans="3:14">
       <c r="C79" s="1">
-        <v>2000217</v>
+        <v>2000208</v>
       </c>
       <c r="D79" s="1">
         <v>2</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="F79" s="4">
+        <v>98</v>
+      </c>
+      <c r="F79" s="1">
         <v>16</v>
       </c>
-      <c r="G79" s="4">
-        <v>2</v>
-      </c>
-      <c r="H79" s="4">
-        <v>2</v>
+      <c r="G79" s="1">
+        <v>1</v>
+      </c>
+      <c r="H79" s="1">
+        <v>1</v>
       </c>
       <c r="I79" s="1">
-        <v>2000217</v>
+        <v>2000208</v>
       </c>
       <c r="J79" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K79" s="1">
         <v>10</v>
       </c>
-      <c r="L79" s="2">
+      <c r="L79" s="3">
         <v>1</v>
       </c>
       <c r="M79" s="1">
         <v>2</v>
       </c>
-      <c r="N79" s="4" t="s">
-        <v>29</v>
+      <c r="N79" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="80" customHeight="1" spans="3:14">
       <c r="C80" s="1">
-        <v>2000218</v>
+        <v>2000209</v>
       </c>
       <c r="D80" s="1">
         <v>2</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F80" s="4">
+        <v>99</v>
+      </c>
+      <c r="F80" s="1">
         <v>16</v>
       </c>
-      <c r="G80" s="4">
-        <v>2</v>
-      </c>
-      <c r="H80" s="4">
-        <v>2</v>
+      <c r="G80" s="1">
+        <v>1</v>
+      </c>
+      <c r="H80" s="1">
+        <v>1</v>
       </c>
       <c r="I80" s="1">
-        <v>2000218</v>
+        <v>2000209</v>
       </c>
       <c r="J80" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K80" s="1">
         <v>10</v>
       </c>
-      <c r="L80" s="2">
+      <c r="L80" s="3">
         <v>1</v>
       </c>
       <c r="M80" s="1">
         <v>2</v>
       </c>
-      <c r="N80" s="4" t="s">
-        <v>29</v>
+      <c r="N80" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="81" customHeight="1" spans="3:14">
       <c r="C81" s="1">
-        <v>2000219</v>
+        <v>2000210</v>
       </c>
       <c r="D81" s="1">
         <v>2</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="F81" s="4">
+        <v>100</v>
+      </c>
+      <c r="F81" s="1">
         <v>16</v>
       </c>
-      <c r="G81" s="4">
-        <v>2</v>
-      </c>
-      <c r="H81" s="4">
-        <v>2</v>
+      <c r="G81" s="1">
+        <v>1</v>
+      </c>
+      <c r="H81" s="1">
+        <v>1</v>
       </c>
       <c r="I81" s="1">
-        <v>2000219</v>
+        <v>2000210</v>
       </c>
       <c r="J81" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K81" s="1">
         <v>10</v>
       </c>
-      <c r="L81" s="2">
+      <c r="L81" s="3">
         <v>1</v>
       </c>
       <c r="M81" s="1">
         <v>2</v>
       </c>
-      <c r="N81" s="4" t="s">
-        <v>29</v>
+      <c r="N81" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="82" customHeight="1" spans="3:14">
       <c r="C82" s="1">
-        <v>2000220</v>
+        <v>2000211</v>
       </c>
       <c r="D82" s="1">
         <v>2</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="F82" s="4">
+        <v>101</v>
+      </c>
+      <c r="F82" s="1">
         <v>16</v>
       </c>
-      <c r="G82" s="4">
-        <v>2</v>
-      </c>
-      <c r="H82" s="4">
-        <v>2</v>
+      <c r="G82" s="1">
+        <v>1</v>
+      </c>
+      <c r="H82" s="1">
+        <v>1</v>
       </c>
       <c r="I82" s="1">
-        <v>2000220</v>
+        <v>2000211</v>
       </c>
       <c r="J82" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K82" s="1">
         <v>10</v>
       </c>
-      <c r="L82" s="2">
+      <c r="L82" s="3">
         <v>1</v>
       </c>
       <c r="M82" s="1">
         <v>2</v>
       </c>
-      <c r="N82" s="4" t="s">
-        <v>29</v>
+      <c r="N82" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="83" customHeight="1" spans="3:14">
       <c r="C83" s="1">
-        <v>2000221</v>
+        <v>2000212</v>
       </c>
       <c r="D83" s="1">
         <v>2</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="F83" s="1">
+        <v>102</v>
+      </c>
+      <c r="F83" s="5">
         <v>15</v>
       </c>
-      <c r="G83" s="1">
-        <v>3</v>
-      </c>
-      <c r="H83" s="1">
-        <v>3</v>
+      <c r="G83" s="5">
+        <v>2</v>
+      </c>
+      <c r="H83" s="5">
+        <v>2</v>
       </c>
       <c r="I83" s="1">
-        <v>2000221</v>
+        <v>2000212</v>
       </c>
       <c r="J83" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K83" s="1">
         <v>10</v>
       </c>
-      <c r="L83" s="2">
+      <c r="L83" s="3">
         <v>1</v>
       </c>
       <c r="M83" s="1">
         <v>2</v>
       </c>
-      <c r="N83" s="7" t="s">
-        <v>25</v>
+      <c r="N83" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="84" customHeight="1" spans="3:14">
       <c r="C84" s="1">
-        <v>2000222</v>
+        <v>2000213</v>
       </c>
       <c r="D84" s="1">
         <v>2</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F84" s="1">
+        <v>103</v>
+      </c>
+      <c r="F84" s="5">
         <v>15</v>
       </c>
-      <c r="G84" s="1">
-        <v>3</v>
-      </c>
-      <c r="H84" s="1">
-        <v>3</v>
+      <c r="G84" s="5">
+        <v>2</v>
+      </c>
+      <c r="H84" s="5">
+        <v>2</v>
       </c>
       <c r="I84" s="1">
-        <v>2000222</v>
+        <v>2000213</v>
       </c>
       <c r="J84" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K84" s="1">
         <v>10</v>
       </c>
-      <c r="L84" s="2">
+      <c r="L84" s="3">
         <v>1</v>
       </c>
       <c r="M84" s="1">
         <v>2</v>
       </c>
-      <c r="N84" s="7" t="s">
-        <v>25</v>
+      <c r="N84" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="85" customHeight="1" spans="3:14">
       <c r="C85" s="1">
-        <v>2000223</v>
+        <v>2000214</v>
       </c>
       <c r="D85" s="1">
         <v>2</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F85" s="1">
+        <v>104</v>
+      </c>
+      <c r="F85" s="5">
         <v>15</v>
       </c>
-      <c r="G85" s="1">
-        <v>3</v>
-      </c>
-      <c r="H85" s="1">
-        <v>3</v>
+      <c r="G85" s="5">
+        <v>2</v>
+      </c>
+      <c r="H85" s="5">
+        <v>2</v>
       </c>
       <c r="I85" s="1">
-        <v>2000223</v>
+        <v>2000214</v>
       </c>
       <c r="J85" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K85" s="1">
         <v>10</v>
       </c>
-      <c r="L85" s="2">
+      <c r="L85" s="3">
         <v>1</v>
       </c>
       <c r="M85" s="1">
         <v>2</v>
       </c>
-      <c r="N85" s="7" t="s">
-        <v>25</v>
+      <c r="N85" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="86" customHeight="1" spans="3:14">
       <c r="C86" s="1">
-        <v>2000224</v>
+        <v>2000215</v>
       </c>
       <c r="D86" s="1">
         <v>2</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="F86" s="1">
+        <v>105</v>
+      </c>
+      <c r="F86" s="5">
         <v>15</v>
       </c>
-      <c r="G86" s="1">
-        <v>3</v>
-      </c>
-      <c r="H86" s="1">
-        <v>3</v>
+      <c r="G86" s="5">
+        <v>2</v>
+      </c>
+      <c r="H86" s="5">
+        <v>2</v>
       </c>
       <c r="I86" s="1">
-        <v>2000224</v>
+        <v>2000215</v>
       </c>
       <c r="J86" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K86" s="1">
         <v>10</v>
       </c>
-      <c r="L86" s="2">
+      <c r="L86" s="3">
         <v>1</v>
       </c>
       <c r="M86" s="1">
         <v>2</v>
       </c>
-      <c r="N86" s="7" t="s">
-        <v>25</v>
+      <c r="N86" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="87" customHeight="1" spans="3:14">
       <c r="C87" s="1">
-        <v>2000225</v>
+        <v>2000216</v>
       </c>
       <c r="D87" s="1">
         <v>2</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F87" s="1">
-        <v>16</v>
-      </c>
-      <c r="G87" s="1">
-        <v>3</v>
-      </c>
-      <c r="H87" s="1">
-        <v>3</v>
+        <v>106</v>
+      </c>
+      <c r="F87" s="5">
+        <v>15</v>
+      </c>
+      <c r="G87" s="5">
+        <v>2</v>
+      </c>
+      <c r="H87" s="5">
+        <v>2</v>
       </c>
       <c r="I87" s="1">
-        <v>2000225</v>
+        <v>2000216</v>
       </c>
       <c r="J87" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K87" s="1">
         <v>10</v>
       </c>
-      <c r="L87" s="2">
+      <c r="L87" s="3">
         <v>1</v>
       </c>
       <c r="M87" s="1">
         <v>2</v>
       </c>
-      <c r="N87" s="7" t="s">
-        <v>29</v>
+      <c r="N87" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="88" customHeight="1" spans="3:14">
       <c r="C88" s="1">
-        <v>2000226</v>
+        <v>2000217</v>
       </c>
       <c r="D88" s="1">
         <v>2</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="F88" s="1">
+        <v>107</v>
+      </c>
+      <c r="F88" s="5">
         <v>16</v>
       </c>
-      <c r="G88" s="1">
-        <v>3</v>
-      </c>
-      <c r="H88" s="1">
-        <v>3</v>
+      <c r="G88" s="5">
+        <v>2</v>
+      </c>
+      <c r="H88" s="5">
+        <v>2</v>
       </c>
       <c r="I88" s="1">
-        <v>2000226</v>
+        <v>2000217</v>
       </c>
       <c r="J88" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K88" s="1">
         <v>10</v>
       </c>
-      <c r="L88" s="2">
+      <c r="L88" s="3">
         <v>1</v>
       </c>
       <c r="M88" s="1">
         <v>2</v>
       </c>
-      <c r="N88" s="7" t="s">
-        <v>29</v>
+      <c r="N88" s="5" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="89" customHeight="1" spans="3:14">
       <c r="C89" s="1">
-        <v>2000227</v>
+        <v>2000218</v>
       </c>
       <c r="D89" s="1">
         <v>2</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F89" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G89" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H89" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I89" s="1">
-        <v>2000227</v>
+        <v>2000218</v>
       </c>
       <c r="J89" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K89" s="1">
         <v>10</v>
       </c>
-      <c r="L89" s="2">
+      <c r="L89" s="3">
         <v>1</v>
       </c>
       <c r="M89" s="1">
         <v>2</v>
       </c>
       <c r="N89" s="5" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="90" customHeight="1" spans="3:14">
       <c r="C90" s="1">
-        <v>2000228</v>
+        <v>2000219</v>
       </c>
       <c r="D90" s="1">
         <v>2</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F90" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G90" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H90" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I90" s="1">
-        <v>2000228</v>
+        <v>2000219</v>
       </c>
       <c r="J90" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K90" s="1">
         <v>10</v>
       </c>
-      <c r="L90" s="2">
+      <c r="L90" s="3">
         <v>1</v>
       </c>
       <c r="M90" s="1">
         <v>2</v>
       </c>
       <c r="N90" s="5" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="91" customHeight="1" spans="3:14">
       <c r="C91" s="1">
-        <v>2000229</v>
+        <v>2000220</v>
       </c>
       <c r="D91" s="1">
         <v>2</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F91" s="5">
         <v>16</v>
       </c>
       <c r="G91" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H91" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I91" s="1">
-        <v>2000229</v>
+        <v>2000220</v>
       </c>
       <c r="J91" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K91" s="1">
         <v>10</v>
       </c>
-      <c r="L91" s="2">
+      <c r="L91" s="3">
         <v>1</v>
       </c>
       <c r="M91" s="1">
         <v>2</v>
       </c>
       <c r="N91" s="5" t="s">
-        <v>29</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="92" customHeight="1" spans="3:14">
+      <c r="C92" s="1">
+        <v>2000221</v>
+      </c>
+      <c r="D92" s="1">
+        <v>2</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F92" s="1">
+        <v>15</v>
+      </c>
+      <c r="G92" s="1">
+        <v>3</v>
+      </c>
+      <c r="H92" s="1">
+        <v>3</v>
+      </c>
+      <c r="I92" s="1">
+        <v>2000221</v>
+      </c>
+      <c r="J92" s="1">
+        <v>3</v>
+      </c>
+      <c r="K92" s="1">
+        <v>10</v>
+      </c>
+      <c r="L92" s="3">
+        <v>1</v>
+      </c>
+      <c r="M92" s="1">
+        <v>2</v>
+      </c>
+      <c r="N92" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="93" customHeight="1" spans="3:14">
+      <c r="C93" s="1">
+        <v>2000222</v>
+      </c>
+      <c r="D93" s="1">
+        <v>2</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F93" s="1">
+        <v>15</v>
+      </c>
+      <c r="G93" s="1">
+        <v>3</v>
+      </c>
+      <c r="H93" s="1">
+        <v>3</v>
+      </c>
+      <c r="I93" s="1">
+        <v>2000222</v>
+      </c>
+      <c r="J93" s="1">
+        <v>3</v>
+      </c>
+      <c r="K93" s="1">
+        <v>10</v>
+      </c>
+      <c r="L93" s="3">
+        <v>1</v>
+      </c>
+      <c r="M93" s="1">
+        <v>2</v>
+      </c>
+      <c r="N93" s="9" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="94" customHeight="1" spans="3:14">
       <c r="C94" s="1">
-        <v>2000300</v>
+        <v>2000223</v>
       </c>
       <c r="D94" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F94" s="1">
         <v>15</v>
       </c>
       <c r="G94" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H94" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I94" s="1">
-        <v>2000300</v>
+        <v>2000223</v>
       </c>
       <c r="J94" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K94" s="1">
         <v>10</v>
       </c>
-      <c r="L94" s="2">
+      <c r="L94" s="3">
         <v>1</v>
       </c>
       <c r="M94" s="1">
         <v>2</v>
       </c>
-      <c r="N94" s="1" t="s">
-        <v>25</v>
+      <c r="N94" s="9" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="95" customHeight="1" spans="3:14">
       <c r="C95" s="1">
-        <v>2000301</v>
+        <v>2000224</v>
       </c>
       <c r="D95" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="F95" s="1">
         <v>15</v>
       </c>
       <c r="G95" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H95" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I95" s="1">
-        <v>2000301</v>
+        <v>2000224</v>
       </c>
       <c r="J95" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K95" s="1">
         <v>10</v>
       </c>
-      <c r="L95" s="2">
+      <c r="L95" s="3">
         <v>1</v>
       </c>
       <c r="M95" s="1">
         <v>2</v>
       </c>
-      <c r="N95" s="1" t="s">
-        <v>25</v>
+      <c r="N95" s="9" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:14">
       <c r="C96" s="1">
-        <v>2000302</v>
+        <v>2000225</v>
       </c>
       <c r="D96" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F96" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G96" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H96" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I96" s="1">
-        <v>2000302</v>
+        <v>2000225</v>
       </c>
       <c r="J96" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K96" s="1">
         <v>10</v>
       </c>
-      <c r="L96" s="2">
+      <c r="L96" s="3">
         <v>1</v>
       </c>
       <c r="M96" s="1">
         <v>2</v>
       </c>
-      <c r="N96" s="1" t="s">
-        <v>25</v>
+      <c r="N96" s="9" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:14">
       <c r="C97" s="1">
-        <v>2000303</v>
+        <v>2000226</v>
       </c>
       <c r="D97" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F97" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G97" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H97" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I97" s="1">
-        <v>2000303</v>
+        <v>2000226</v>
       </c>
       <c r="J97" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K97" s="1">
         <v>10</v>
       </c>
-      <c r="L97" s="2">
+      <c r="L97" s="3">
         <v>1</v>
       </c>
       <c r="M97" s="1">
         <v>2</v>
       </c>
-      <c r="N97" s="1" t="s">
-        <v>25</v>
+      <c r="N97" s="9" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:14">
       <c r="C98" s="1">
-        <v>2000304</v>
+        <v>2000227</v>
       </c>
       <c r="D98" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F98" s="1">
-        <v>14</v>
-      </c>
-      <c r="G98" s="1">
-        <v>1</v>
-      </c>
-      <c r="H98" s="1">
-        <v>1</v>
+        <v>117</v>
+      </c>
+      <c r="F98" s="6">
+        <v>15</v>
+      </c>
+      <c r="G98" s="6">
+        <v>4</v>
+      </c>
+      <c r="H98" s="6">
+        <v>4</v>
       </c>
       <c r="I98" s="1">
-        <v>2000304</v>
+        <v>2000227</v>
       </c>
       <c r="J98" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K98" s="1">
         <v>10</v>
       </c>
-      <c r="L98" s="2">
+      <c r="L98" s="3">
         <v>1</v>
       </c>
       <c r="M98" s="1">
         <v>2</v>
       </c>
-      <c r="N98" s="1" t="s">
-        <v>27</v>
+      <c r="N98" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:14">
       <c r="C99" s="1">
-        <v>2000305</v>
+        <v>2000228</v>
       </c>
       <c r="D99" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F99" s="1">
-        <v>14</v>
-      </c>
-      <c r="G99" s="1">
-        <v>1</v>
-      </c>
-      <c r="H99" s="1">
-        <v>1</v>
+        <v>118</v>
+      </c>
+      <c r="F99" s="6">
+        <v>15</v>
+      </c>
+      <c r="G99" s="6">
+        <v>4</v>
+      </c>
+      <c r="H99" s="6">
+        <v>4</v>
       </c>
       <c r="I99" s="1">
-        <v>2000305</v>
+        <v>2000228</v>
       </c>
       <c r="J99" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K99" s="1">
         <v>10</v>
       </c>
-      <c r="L99" s="2">
+      <c r="L99" s="3">
         <v>1</v>
       </c>
       <c r="M99" s="1">
         <v>2</v>
       </c>
-      <c r="N99" s="1" t="s">
-        <v>27</v>
+      <c r="N99" s="6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:14">
       <c r="C100" s="1">
-        <v>2000306</v>
+        <v>2000229</v>
       </c>
       <c r="D100" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F100" s="1">
-        <v>14</v>
-      </c>
-      <c r="G100" s="1">
-        <v>1</v>
-      </c>
-      <c r="H100" s="1">
-        <v>1</v>
+        <v>119</v>
+      </c>
+      <c r="F100" s="6">
+        <v>16</v>
+      </c>
+      <c r="G100" s="6">
+        <v>4</v>
+      </c>
+      <c r="H100" s="6">
+        <v>4</v>
       </c>
       <c r="I100" s="1">
-        <v>2000306</v>
+        <v>2000229</v>
       </c>
       <c r="J100" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K100" s="1">
         <v>10</v>
       </c>
-      <c r="L100" s="2">
+      <c r="L100" s="3">
         <v>1</v>
       </c>
       <c r="M100" s="1">
         <v>2</v>
       </c>
-      <c r="N100" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="101" customHeight="1" spans="3:14">
-      <c r="C101" s="1">
-        <v>2000307</v>
-      </c>
-      <c r="D101" s="1">
-        <v>3</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F101" s="1">
-        <v>14</v>
-      </c>
-      <c r="G101" s="1">
-        <v>1</v>
-      </c>
-      <c r="H101" s="1">
-        <v>1</v>
-      </c>
-      <c r="I101" s="1">
-        <v>2000307</v>
-      </c>
-      <c r="J101" s="1">
-        <v>1</v>
-      </c>
-      <c r="K101" s="1">
-        <v>10</v>
-      </c>
-      <c r="L101" s="2">
-        <v>1</v>
-      </c>
-      <c r="M101" s="1">
-        <v>2</v>
-      </c>
-      <c r="N101" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="102" customHeight="1" spans="3:14">
-      <c r="C102" s="1">
-        <v>2000308</v>
-      </c>
-      <c r="D102" s="1">
-        <v>3</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="F102" s="1">
-        <v>16</v>
-      </c>
-      <c r="G102" s="1">
-        <v>1</v>
-      </c>
-      <c r="H102" s="1">
-        <v>1</v>
-      </c>
-      <c r="I102" s="1">
-        <v>2000308</v>
-      </c>
-      <c r="J102" s="1">
-        <v>1</v>
-      </c>
-      <c r="K102" s="1">
-        <v>10</v>
-      </c>
-      <c r="L102" s="2">
-        <v>1</v>
-      </c>
-      <c r="M102" s="1">
-        <v>2</v>
-      </c>
-      <c r="N102" s="1" t="s">
-        <v>29</v>
+      <c r="N100" s="6" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:14">
       <c r="C103" s="1">
-        <v>2000309</v>
+        <v>2000300</v>
       </c>
       <c r="D103" s="1">
         <v>3</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F103" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G103" s="1">
         <v>1</v>
@@ -5248,7 +5519,7 @@
         <v>1</v>
       </c>
       <c r="I103" s="1">
-        <v>2000309</v>
+        <v>2000300</v>
       </c>
       <c r="J103" s="1">
         <v>1</v>
@@ -5256,28 +5527,28 @@
       <c r="K103" s="1">
         <v>10</v>
       </c>
-      <c r="L103" s="2">
+      <c r="L103" s="3">
         <v>1</v>
       </c>
       <c r="M103" s="1">
         <v>2</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:14">
       <c r="C104" s="1">
-        <v>2000310</v>
+        <v>2000301</v>
       </c>
       <c r="D104" s="1">
         <v>3</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F104" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G104" s="1">
         <v>1</v>
@@ -5286,7 +5557,7 @@
         <v>1</v>
       </c>
       <c r="I104" s="1">
-        <v>2000310</v>
+        <v>2000301</v>
       </c>
       <c r="J104" s="1">
         <v>1</v>
@@ -5294,28 +5565,28 @@
       <c r="K104" s="1">
         <v>10</v>
       </c>
-      <c r="L104" s="2">
+      <c r="L104" s="3">
         <v>1</v>
       </c>
       <c r="M104" s="1">
         <v>2</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:14">
       <c r="C105" s="1">
-        <v>2000311</v>
+        <v>2000302</v>
       </c>
       <c r="D105" s="1">
         <v>3</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F105" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G105" s="1">
         <v>1</v>
@@ -5324,7 +5595,7 @@
         <v>1</v>
       </c>
       <c r="I105" s="1">
-        <v>2000311</v>
+        <v>2000302</v>
       </c>
       <c r="J105" s="1">
         <v>1</v>
@@ -5332,698 +5603,1040 @@
       <c r="K105" s="1">
         <v>10</v>
       </c>
-      <c r="L105" s="2">
+      <c r="L105" s="3">
         <v>1</v>
       </c>
       <c r="M105" s="1">
         <v>2</v>
       </c>
       <c r="N105" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:14">
       <c r="C106" s="1">
-        <v>2000312</v>
+        <v>2000303</v>
       </c>
       <c r="D106" s="1">
         <v>3</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F106" s="4">
+        <v>123</v>
+      </c>
+      <c r="F106" s="1">
         <v>15</v>
       </c>
-      <c r="G106" s="4">
-        <v>2</v>
-      </c>
-      <c r="H106" s="4">
-        <v>2</v>
+      <c r="G106" s="1">
+        <v>1</v>
+      </c>
+      <c r="H106" s="1">
+        <v>1</v>
       </c>
       <c r="I106" s="1">
-        <v>2000312</v>
+        <v>2000303</v>
       </c>
       <c r="J106" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K106" s="1">
         <v>10</v>
       </c>
-      <c r="L106" s="2">
+      <c r="L106" s="3">
         <v>1</v>
       </c>
       <c r="M106" s="1">
         <v>2</v>
       </c>
-      <c r="N106" s="4" t="s">
-        <v>25</v>
+      <c r="N106" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:14">
       <c r="C107" s="1">
-        <v>2000313</v>
+        <v>2000304</v>
       </c>
       <c r="D107" s="1">
         <v>3</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="F107" s="4">
-        <v>15</v>
-      </c>
-      <c r="G107" s="4">
-        <v>2</v>
-      </c>
-      <c r="H107" s="4">
-        <v>2</v>
+        <v>124</v>
+      </c>
+      <c r="F107" s="1">
+        <v>14</v>
+      </c>
+      <c r="G107" s="1">
+        <v>1</v>
+      </c>
+      <c r="H107" s="1">
+        <v>1</v>
       </c>
       <c r="I107" s="1">
-        <v>2000313</v>
+        <v>2000304</v>
       </c>
       <c r="J107" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K107" s="1">
         <v>10</v>
       </c>
-      <c r="L107" s="2">
+      <c r="L107" s="3">
         <v>1</v>
       </c>
       <c r="M107" s="1">
         <v>2</v>
       </c>
-      <c r="N107" s="4" t="s">
-        <v>25</v>
+      <c r="N107" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:14">
       <c r="C108" s="1">
-        <v>2000314</v>
+        <v>2000305</v>
       </c>
       <c r="D108" s="1">
         <v>3</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="F108" s="4">
-        <v>15</v>
-      </c>
-      <c r="G108" s="4">
-        <v>2</v>
-      </c>
-      <c r="H108" s="4">
-        <v>2</v>
+        <v>125</v>
+      </c>
+      <c r="F108" s="1">
+        <v>14</v>
+      </c>
+      <c r="G108" s="1">
+        <v>1</v>
+      </c>
+      <c r="H108" s="1">
+        <v>1</v>
       </c>
       <c r="I108" s="1">
-        <v>2000314</v>
+        <v>2000305</v>
       </c>
       <c r="J108" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K108" s="1">
         <v>10</v>
       </c>
-      <c r="L108" s="2">
+      <c r="L108" s="3">
         <v>1</v>
       </c>
       <c r="M108" s="1">
         <v>2</v>
       </c>
-      <c r="N108" s="4" t="s">
-        <v>25</v>
+      <c r="N108" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:14">
       <c r="C109" s="1">
-        <v>2000315</v>
+        <v>2000306</v>
       </c>
       <c r="D109" s="1">
         <v>3</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F109" s="4">
+        <v>126</v>
+      </c>
+      <c r="F109" s="1">
         <v>14</v>
       </c>
-      <c r="G109" s="4">
-        <v>2</v>
-      </c>
-      <c r="H109" s="4">
-        <v>2</v>
+      <c r="G109" s="1">
+        <v>1</v>
+      </c>
+      <c r="H109" s="1">
+        <v>1</v>
       </c>
       <c r="I109" s="1">
-        <v>2000315</v>
+        <v>2000306</v>
       </c>
       <c r="J109" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K109" s="1">
         <v>10</v>
       </c>
-      <c r="L109" s="2">
+      <c r="L109" s="3">
         <v>1</v>
       </c>
       <c r="M109" s="1">
         <v>2</v>
       </c>
-      <c r="N109" s="4" t="s">
-        <v>27</v>
+      <c r="N109" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:14">
       <c r="C110" s="1">
-        <v>2000316</v>
+        <v>2000307</v>
       </c>
       <c r="D110" s="1">
         <v>3</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F110" s="4">
+        <v>127</v>
+      </c>
+      <c r="F110" s="1">
         <v>14</v>
       </c>
-      <c r="G110" s="4">
-        <v>2</v>
-      </c>
-      <c r="H110" s="4">
-        <v>2</v>
+      <c r="G110" s="1">
+        <v>1</v>
+      </c>
+      <c r="H110" s="1">
+        <v>1</v>
       </c>
       <c r="I110" s="1">
-        <v>2000316</v>
+        <v>2000307</v>
       </c>
       <c r="J110" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K110" s="1">
         <v>10</v>
       </c>
-      <c r="L110" s="2">
+      <c r="L110" s="3">
         <v>1</v>
       </c>
       <c r="M110" s="1">
         <v>2</v>
       </c>
-      <c r="N110" s="4" t="s">
-        <v>27</v>
+      <c r="N110" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:14">
       <c r="C111" s="1">
-        <v>2000317</v>
+        <v>2000308</v>
       </c>
       <c r="D111" s="1">
         <v>3</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F111" s="4">
-        <v>14</v>
-      </c>
-      <c r="G111" s="4">
-        <v>2</v>
-      </c>
-      <c r="H111" s="4">
-        <v>2</v>
+        <v>128</v>
+      </c>
+      <c r="F111" s="1">
+        <v>16</v>
+      </c>
+      <c r="G111" s="1">
+        <v>1</v>
+      </c>
+      <c r="H111" s="1">
+        <v>1</v>
       </c>
       <c r="I111" s="1">
-        <v>2000317</v>
+        <v>2000308</v>
       </c>
       <c r="J111" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K111" s="1">
         <v>10</v>
       </c>
-      <c r="L111" s="2">
+      <c r="L111" s="3">
         <v>1</v>
       </c>
       <c r="M111" s="1">
         <v>2</v>
       </c>
-      <c r="N111" s="4" t="s">
-        <v>27</v>
+      <c r="N111" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:14">
       <c r="C112" s="1">
-        <v>2000318</v>
+        <v>2000309</v>
       </c>
       <c r="D112" s="1">
         <v>3</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="F112" s="4">
+        <v>129</v>
+      </c>
+      <c r="F112" s="1">
         <v>16</v>
       </c>
-      <c r="G112" s="4">
-        <v>2</v>
-      </c>
-      <c r="H112" s="4">
-        <v>2</v>
+      <c r="G112" s="1">
+        <v>1</v>
+      </c>
+      <c r="H112" s="1">
+        <v>1</v>
       </c>
       <c r="I112" s="1">
-        <v>2000318</v>
+        <v>2000309</v>
       </c>
       <c r="J112" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K112" s="1">
         <v>10</v>
       </c>
-      <c r="L112" s="2">
+      <c r="L112" s="3">
         <v>1</v>
       </c>
       <c r="M112" s="1">
         <v>2</v>
       </c>
-      <c r="N112" s="4" t="s">
-        <v>29</v>
+      <c r="N112" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="3:14">
       <c r="C113" s="1">
-        <v>2000319</v>
+        <v>2000310</v>
       </c>
       <c r="D113" s="1">
         <v>3</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="F113" s="4">
+        <v>130</v>
+      </c>
+      <c r="F113" s="1">
         <v>16</v>
       </c>
-      <c r="G113" s="4">
-        <v>2</v>
-      </c>
-      <c r="H113" s="4">
-        <v>2</v>
+      <c r="G113" s="1">
+        <v>1</v>
+      </c>
+      <c r="H113" s="1">
+        <v>1</v>
       </c>
       <c r="I113" s="1">
-        <v>2000319</v>
+        <v>2000310</v>
       </c>
       <c r="J113" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K113" s="1">
         <v>10</v>
       </c>
-      <c r="L113" s="2">
+      <c r="L113" s="3">
         <v>1</v>
       </c>
       <c r="M113" s="1">
         <v>2</v>
       </c>
-      <c r="N113" s="4" t="s">
-        <v>29</v>
+      <c r="N113" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="114" customHeight="1" spans="3:14">
       <c r="C114" s="1">
-        <v>2000320</v>
+        <v>2000311</v>
       </c>
       <c r="D114" s="1">
         <v>3</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="F114" s="4">
+        <v>131</v>
+      </c>
+      <c r="F114" s="1">
         <v>16</v>
       </c>
-      <c r="G114" s="4">
-        <v>2</v>
-      </c>
-      <c r="H114" s="4">
-        <v>2</v>
+      <c r="G114" s="1">
+        <v>1</v>
+      </c>
+      <c r="H114" s="1">
+        <v>1</v>
       </c>
       <c r="I114" s="1">
-        <v>2000320</v>
+        <v>2000311</v>
       </c>
       <c r="J114" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K114" s="1">
         <v>10</v>
       </c>
-      <c r="L114" s="2">
+      <c r="L114" s="3">
         <v>1</v>
       </c>
       <c r="M114" s="1">
         <v>2</v>
       </c>
-      <c r="N114" s="4" t="s">
-        <v>29</v>
+      <c r="N114" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="115" customHeight="1" spans="3:14">
       <c r="C115" s="1">
-        <v>2000321</v>
+        <v>2000312</v>
       </c>
       <c r="D115" s="1">
         <v>3</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F115" s="1">
+        <v>132</v>
+      </c>
+      <c r="F115" s="5">
         <v>15</v>
       </c>
-      <c r="G115" s="1">
-        <v>3</v>
-      </c>
-      <c r="H115" s="1">
-        <v>3</v>
+      <c r="G115" s="5">
+        <v>2</v>
+      </c>
+      <c r="H115" s="5">
+        <v>2</v>
       </c>
       <c r="I115" s="1">
-        <v>2000321</v>
+        <v>2000312</v>
       </c>
       <c r="J115" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K115" s="1">
         <v>10</v>
       </c>
-      <c r="L115" s="2">
+      <c r="L115" s="3">
         <v>1</v>
       </c>
       <c r="M115" s="1">
         <v>2</v>
       </c>
-      <c r="N115" s="7" t="s">
-        <v>25</v>
+      <c r="N115" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="3:14">
       <c r="C116" s="1">
-        <v>2000322</v>
+        <v>2000313</v>
       </c>
       <c r="D116" s="1">
         <v>3</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="F116" s="1">
+        <v>133</v>
+      </c>
+      <c r="F116" s="5">
         <v>15</v>
       </c>
-      <c r="G116" s="1">
-        <v>3</v>
-      </c>
-      <c r="H116" s="1">
-        <v>3</v>
+      <c r="G116" s="5">
+        <v>2</v>
+      </c>
+      <c r="H116" s="5">
+        <v>2</v>
       </c>
       <c r="I116" s="1">
-        <v>2000322</v>
+        <v>2000313</v>
       </c>
       <c r="J116" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K116" s="1">
         <v>10</v>
       </c>
-      <c r="L116" s="2">
+      <c r="L116" s="3">
         <v>1</v>
       </c>
       <c r="M116" s="1">
         <v>2</v>
       </c>
-      <c r="N116" s="7" t="s">
-        <v>25</v>
+      <c r="N116" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="3:14">
       <c r="C117" s="1">
-        <v>2000323</v>
+        <v>2000314</v>
       </c>
       <c r="D117" s="1">
         <v>3</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="F117" s="1">
-        <v>14</v>
-      </c>
-      <c r="G117" s="1">
-        <v>3</v>
-      </c>
-      <c r="H117" s="1">
-        <v>3</v>
+        <v>134</v>
+      </c>
+      <c r="F117" s="5">
+        <v>15</v>
+      </c>
+      <c r="G117" s="5">
+        <v>2</v>
+      </c>
+      <c r="H117" s="5">
+        <v>2</v>
       </c>
       <c r="I117" s="1">
-        <v>2000323</v>
+        <v>2000314</v>
       </c>
       <c r="J117" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K117" s="1">
         <v>10</v>
       </c>
-      <c r="L117" s="2">
+      <c r="L117" s="3">
         <v>1</v>
       </c>
       <c r="M117" s="1">
         <v>2</v>
       </c>
-      <c r="N117" s="7" t="s">
-        <v>27</v>
+      <c r="N117" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="3:14">
       <c r="C118" s="1">
-        <v>2000324</v>
+        <v>2000315</v>
       </c>
       <c r="D118" s="1">
         <v>3</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F118" s="1">
+        <v>135</v>
+      </c>
+      <c r="F118" s="5">
         <v>14</v>
       </c>
-      <c r="G118" s="1">
-        <v>3</v>
-      </c>
-      <c r="H118" s="1">
-        <v>3</v>
+      <c r="G118" s="5">
+        <v>2</v>
+      </c>
+      <c r="H118" s="5">
+        <v>2</v>
       </c>
       <c r="I118" s="1">
-        <v>2000324</v>
+        <v>2000315</v>
       </c>
       <c r="J118" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K118" s="1">
         <v>10</v>
       </c>
-      <c r="L118" s="2">
+      <c r="L118" s="3">
         <v>1</v>
       </c>
       <c r="M118" s="1">
         <v>2</v>
       </c>
-      <c r="N118" s="7" t="s">
-        <v>27</v>
+      <c r="N118" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="3:14">
       <c r="C119" s="1">
-        <v>2000325</v>
+        <v>2000316</v>
       </c>
       <c r="D119" s="1">
         <v>3</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="F119" s="1">
-        <v>16</v>
-      </c>
-      <c r="G119" s="1">
-        <v>3</v>
-      </c>
-      <c r="H119" s="1">
-        <v>3</v>
+        <v>136</v>
+      </c>
+      <c r="F119" s="5">
+        <v>14</v>
+      </c>
+      <c r="G119" s="5">
+        <v>2</v>
+      </c>
+      <c r="H119" s="5">
+        <v>2</v>
       </c>
       <c r="I119" s="1">
-        <v>2000325</v>
+        <v>2000316</v>
       </c>
       <c r="J119" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K119" s="1">
         <v>10</v>
       </c>
-      <c r="L119" s="2">
+      <c r="L119" s="3">
         <v>1</v>
       </c>
       <c r="M119" s="1">
         <v>2</v>
       </c>
-      <c r="N119" s="7" t="s">
-        <v>29</v>
+      <c r="N119" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="3:14">
       <c r="C120" s="1">
-        <v>2000326</v>
+        <v>2000317</v>
       </c>
       <c r="D120" s="1">
         <v>3</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="F120" s="1">
-        <v>16</v>
-      </c>
-      <c r="G120" s="1">
-        <v>3</v>
-      </c>
-      <c r="H120" s="1">
-        <v>3</v>
+        <v>137</v>
+      </c>
+      <c r="F120" s="5">
+        <v>14</v>
+      </c>
+      <c r="G120" s="5">
+        <v>2</v>
+      </c>
+      <c r="H120" s="5">
+        <v>2</v>
       </c>
       <c r="I120" s="1">
-        <v>2000326</v>
+        <v>2000317</v>
       </c>
       <c r="J120" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K120" s="1">
         <v>10</v>
       </c>
-      <c r="L120" s="2">
+      <c r="L120" s="3">
         <v>1</v>
       </c>
       <c r="M120" s="1">
         <v>2</v>
       </c>
-      <c r="N120" s="7" t="s">
-        <v>29</v>
+      <c r="N120" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="121" customHeight="1" spans="3:14">
       <c r="C121" s="1">
-        <v>2000327</v>
+        <v>2000318</v>
       </c>
       <c r="D121" s="1">
         <v>3</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F121" s="5">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G121" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H121" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I121" s="1">
-        <v>2000327</v>
+        <v>2000318</v>
       </c>
       <c r="J121" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K121" s="1">
         <v>10</v>
       </c>
-      <c r="L121" s="2">
+      <c r="L121" s="3">
         <v>1</v>
       </c>
       <c r="M121" s="1">
         <v>2</v>
       </c>
       <c r="N121" s="5" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="122" customHeight="1" spans="3:14">
       <c r="C122" s="1">
-        <v>2000328</v>
+        <v>2000319</v>
       </c>
       <c r="D122" s="1">
         <v>3</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="F122" s="5">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G122" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H122" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I122" s="1">
-        <v>2000328</v>
+        <v>2000319</v>
       </c>
       <c r="J122" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K122" s="1">
         <v>10</v>
       </c>
-      <c r="L122" s="2">
+      <c r="L122" s="3">
         <v>1</v>
       </c>
       <c r="M122" s="1">
         <v>2</v>
       </c>
       <c r="N122" s="5" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
     </row>
     <row r="123" customHeight="1" spans="3:14">
       <c r="C123" s="1">
-        <v>2000329</v>
+        <v>2000320</v>
       </c>
       <c r="D123" s="1">
         <v>3</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="F123" s="5">
         <v>16</v>
       </c>
       <c r="G123" s="5">
+        <v>2</v>
+      </c>
+      <c r="H123" s="5">
+        <v>2</v>
+      </c>
+      <c r="I123" s="1">
+        <v>2000320</v>
+      </c>
+      <c r="J123" s="1">
+        <v>2</v>
+      </c>
+      <c r="K123" s="1">
+        <v>10</v>
+      </c>
+      <c r="L123" s="3">
+        <v>1</v>
+      </c>
+      <c r="M123" s="1">
+        <v>2</v>
+      </c>
+      <c r="N123" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="124" customHeight="1" spans="3:14">
+      <c r="C124" s="1">
+        <v>2000321</v>
+      </c>
+      <c r="D124" s="1">
+        <v>3</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F124" s="1">
+        <v>15</v>
+      </c>
+      <c r="G124" s="1">
+        <v>3</v>
+      </c>
+      <c r="H124" s="1">
+        <v>3</v>
+      </c>
+      <c r="I124" s="1">
+        <v>2000321</v>
+      </c>
+      <c r="J124" s="1">
+        <v>3</v>
+      </c>
+      <c r="K124" s="1">
+        <v>10</v>
+      </c>
+      <c r="L124" s="3">
+        <v>1</v>
+      </c>
+      <c r="M124" s="1">
+        <v>2</v>
+      </c>
+      <c r="N124" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="125" customHeight="1" spans="3:14">
+      <c r="C125" s="1">
+        <v>2000322</v>
+      </c>
+      <c r="D125" s="1">
+        <v>3</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F125" s="1">
+        <v>15</v>
+      </c>
+      <c r="G125" s="1">
+        <v>3</v>
+      </c>
+      <c r="H125" s="1">
+        <v>3</v>
+      </c>
+      <c r="I125" s="1">
+        <v>2000322</v>
+      </c>
+      <c r="J125" s="1">
+        <v>3</v>
+      </c>
+      <c r="K125" s="1">
+        <v>10</v>
+      </c>
+      <c r="L125" s="3">
+        <v>1</v>
+      </c>
+      <c r="M125" s="1">
+        <v>2</v>
+      </c>
+      <c r="N125" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="126" customHeight="1" spans="3:14">
+      <c r="C126" s="1">
+        <v>2000323</v>
+      </c>
+      <c r="D126" s="1">
+        <v>3</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F126" s="1">
+        <v>14</v>
+      </c>
+      <c r="G126" s="1">
+        <v>3</v>
+      </c>
+      <c r="H126" s="1">
+        <v>3</v>
+      </c>
+      <c r="I126" s="1">
+        <v>2000323</v>
+      </c>
+      <c r="J126" s="1">
+        <v>3</v>
+      </c>
+      <c r="K126" s="1">
+        <v>10</v>
+      </c>
+      <c r="L126" s="3">
+        <v>1</v>
+      </c>
+      <c r="M126" s="1">
+        <v>2</v>
+      </c>
+      <c r="N126" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="127" customHeight="1" spans="3:14">
+      <c r="C127" s="1">
+        <v>2000324</v>
+      </c>
+      <c r="D127" s="1">
+        <v>3</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F127" s="1">
+        <v>14</v>
+      </c>
+      <c r="G127" s="1">
+        <v>3</v>
+      </c>
+      <c r="H127" s="1">
+        <v>3</v>
+      </c>
+      <c r="I127" s="1">
+        <v>2000324</v>
+      </c>
+      <c r="J127" s="1">
+        <v>3</v>
+      </c>
+      <c r="K127" s="1">
+        <v>10</v>
+      </c>
+      <c r="L127" s="3">
+        <v>1</v>
+      </c>
+      <c r="M127" s="1">
+        <v>2</v>
+      </c>
+      <c r="N127" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="128" customHeight="1" spans="3:14">
+      <c r="C128" s="1">
+        <v>2000325</v>
+      </c>
+      <c r="D128" s="1">
+        <v>3</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F128" s="1">
+        <v>16</v>
+      </c>
+      <c r="G128" s="1">
+        <v>3</v>
+      </c>
+      <c r="H128" s="1">
+        <v>3</v>
+      </c>
+      <c r="I128" s="1">
+        <v>2000325</v>
+      </c>
+      <c r="J128" s="1">
+        <v>3</v>
+      </c>
+      <c r="K128" s="1">
+        <v>10</v>
+      </c>
+      <c r="L128" s="3">
+        <v>1</v>
+      </c>
+      <c r="M128" s="1">
+        <v>2</v>
+      </c>
+      <c r="N128" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="129" customHeight="1" spans="3:14">
+      <c r="C129" s="1">
+        <v>2000326</v>
+      </c>
+      <c r="D129" s="1">
+        <v>3</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F129" s="1">
+        <v>16</v>
+      </c>
+      <c r="G129" s="1">
+        <v>3</v>
+      </c>
+      <c r="H129" s="1">
+        <v>3</v>
+      </c>
+      <c r="I129" s="1">
+        <v>2000326</v>
+      </c>
+      <c r="J129" s="1">
+        <v>3</v>
+      </c>
+      <c r="K129" s="1">
+        <v>10</v>
+      </c>
+      <c r="L129" s="3">
+        <v>1</v>
+      </c>
+      <c r="M129" s="1">
+        <v>2</v>
+      </c>
+      <c r="N129" s="9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="3:14">
+      <c r="C130" s="1">
+        <v>2000327</v>
+      </c>
+      <c r="D130" s="1">
+        <v>3</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F130" s="6">
+        <v>15</v>
+      </c>
+      <c r="G130" s="6">
         <v>4</v>
       </c>
-      <c r="H123" s="5">
+      <c r="H130" s="6">
         <v>4</v>
       </c>
-      <c r="I123" s="1">
+      <c r="I130" s="1">
+        <v>2000327</v>
+      </c>
+      <c r="J130" s="1">
+        <v>4</v>
+      </c>
+      <c r="K130" s="1">
+        <v>10</v>
+      </c>
+      <c r="L130" s="3">
+        <v>1</v>
+      </c>
+      <c r="M130" s="1">
+        <v>2</v>
+      </c>
+      <c r="N130" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="131" customHeight="1" spans="3:14">
+      <c r="C131" s="1">
+        <v>2000328</v>
+      </c>
+      <c r="D131" s="1">
+        <v>3</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F131" s="6">
+        <v>14</v>
+      </c>
+      <c r="G131" s="6">
+        <v>4</v>
+      </c>
+      <c r="H131" s="6">
+        <v>4</v>
+      </c>
+      <c r="I131" s="1">
+        <v>2000328</v>
+      </c>
+      <c r="J131" s="1">
+        <v>4</v>
+      </c>
+      <c r="K131" s="1">
+        <v>10</v>
+      </c>
+      <c r="L131" s="3">
+        <v>1</v>
+      </c>
+      <c r="M131" s="1">
+        <v>2</v>
+      </c>
+      <c r="N131" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="3:14">
+      <c r="C132" s="1">
         <v>2000329</v>
       </c>
-      <c r="J123" s="1">
+      <c r="D132" s="1">
+        <v>3</v>
+      </c>
+      <c r="E132" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F132" s="6">
+        <v>16</v>
+      </c>
+      <c r="G132" s="6">
         <v>4</v>
       </c>
-      <c r="K123" s="1">
-        <v>10</v>
-      </c>
-      <c r="L123" s="2">
-        <v>1</v>
-      </c>
-      <c r="M123" s="1">
-        <v>2</v>
-      </c>
-      <c r="N123" s="5" t="s">
-        <v>29</v>
+      <c r="H132" s="6">
+        <v>4</v>
+      </c>
+      <c r="I132" s="1">
+        <v>2000329</v>
+      </c>
+      <c r="J132" s="1">
+        <v>4</v>
+      </c>
+      <c r="K132" s="1">
+        <v>10</v>
+      </c>
+      <c r="L132" s="3">
+        <v>1</v>
+      </c>
+      <c r="M132" s="1">
+        <v>2</v>
+      </c>
+      <c r="N132" s="6" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -74,37 +74,37 @@
     <t>神鉴·白</t>
   </si>
   <si>
-    <t>白色图鉴等级+1%</t>
+    <t>白图鉴等级+1%</t>
   </si>
   <si>
     <t>神鉴·绿</t>
   </si>
   <si>
-    <t>绿色图鉴等级+1%</t>
+    <t>绿图鉴等级+1%</t>
   </si>
   <si>
     <t>神鉴·蓝</t>
   </si>
   <si>
-    <t>蓝色图鉴等级+1%</t>
+    <t>蓝图鉴等级+1%</t>
   </si>
   <si>
     <t>神鉴·紫</t>
   </si>
   <si>
-    <t>紫色图鉴等级+1%</t>
+    <t>紫图鉴等级+1%</t>
   </si>
   <si>
     <t>神鉴·橙</t>
   </si>
   <si>
-    <t>橙色图鉴等级+1%</t>
+    <t>橙图鉴等级+1%</t>
   </si>
   <si>
     <t>神鉴·红</t>
   </si>
   <si>
-    <t>红色图鉴等级+1%</t>
+    <t>红图鉴等级+1%</t>
   </si>
   <si>
     <t>龙之怒</t>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -1679,7 +1679,7 @@
         <v>7</v>
       </c>
       <c r="J7" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2">
         <v>1</v>
@@ -1720,7 +1720,7 @@
         <v>7</v>
       </c>
       <c r="J8" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2">
         <v>1</v>
@@ -1761,7 +1761,7 @@
         <v>7</v>
       </c>
       <c r="J9" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K9" s="2">
         <v>1</v>
@@ -1802,7 +1802,7 @@
         <v>7</v>
       </c>
       <c r="J10" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K10" s="2">
         <v>1</v>
@@ -1843,7 +1843,7 @@
         <v>7</v>
       </c>
       <c r="J11" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K11" s="2">
         <v>1</v>
@@ -1884,7 +1884,7 @@
         <v>7</v>
       </c>
       <c r="J12" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K12" s="2">
         <v>1</v>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -2904,7 +2904,7 @@
         <v>1</v>
       </c>
       <c r="H36" s="2">
-        <v>2000010</v>
+        <v>2000011</v>
       </c>
       <c r="I36" s="2">
         <v>5</v>
@@ -2955,7 +2955,7 @@
         <v>1</v>
       </c>
       <c r="H37" s="2">
-        <v>2000010</v>
+        <v>2000012</v>
       </c>
       <c r="I37" s="2">
         <v>5</v>
@@ -3006,7 +3006,7 @@
         <v>1</v>
       </c>
       <c r="H38" s="2">
-        <v>2000010</v>
+        <v>2000013</v>
       </c>
       <c r="I38" s="2">
         <v>5</v>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27952" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="定制配置" sheetId="2" r:id="rId1"/>
@@ -74,37 +74,37 @@
     <t>神鉴·白</t>
   </si>
   <si>
-    <t>白图鉴等级+1%</t>
+    <t>白图鉴等级+{0}%</t>
   </si>
   <si>
     <t>神鉴·绿</t>
   </si>
   <si>
-    <t>绿图鉴等级+1%</t>
+    <t>绿图鉴等级+{0}%</t>
   </si>
   <si>
     <t>神鉴·蓝</t>
   </si>
   <si>
-    <t>蓝图鉴等级+1%</t>
+    <t>蓝图鉴等级+{0}%</t>
   </si>
   <si>
     <t>神鉴·紫</t>
   </si>
   <si>
-    <t>紫图鉴等级+1%</t>
+    <t>紫图鉴等级+{0}%</t>
   </si>
   <si>
     <t>神鉴·橙</t>
   </si>
   <si>
-    <t>橙图鉴等级+1%</t>
+    <t>橙图鉴等级+{0}%</t>
   </si>
   <si>
     <t>神鉴·红</t>
   </si>
   <si>
-    <t>红图鉴等级+1%</t>
+    <t>红图鉴等级+{0}%</t>
   </si>
   <si>
     <t>龙之怒</t>
@@ -1530,9 +1530,9 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="12.625" style="1" customWidth="1"/>
-    <col min="6" max="13" width="12.25" style="1" customWidth="1"/>
-    <col min="14" max="14" width="26.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12.6283185840708" style="1" customWidth="1"/>
+    <col min="6" max="13" width="12.2477876106195" style="1" customWidth="1"/>
+    <col min="14" max="14" width="26.7522123893805" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>

--- a/Excel/CardConfig.xlsx
+++ b/Excel/CardConfig.xlsx
@@ -3198,7 +3198,7 @@
         <v>1</v>
       </c>
       <c r="J44" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K44" s="2">
         <v>1</v>
@@ -3249,7 +3249,7 @@
         <v>1</v>
       </c>
       <c r="J45" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K45" s="2">
         <v>1</v>
@@ -3298,7 +3298,7 @@
         <v>1</v>
       </c>
       <c r="J46" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K46" s="2">
         <v>1</v>
@@ -3336,7 +3336,7 @@
         <v>1</v>
       </c>
       <c r="J47" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K47" s="2">
         <v>1</v>
@@ -3374,7 +3374,7 @@
         <v>1</v>
       </c>
       <c r="J48" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K48" s="2">
         <v>1</v>
@@ -3412,7 +3412,7 @@
         <v>1</v>
       </c>
       <c r="J49" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K49" s="2">
         <v>1</v>
@@ -3450,7 +3450,7 @@
         <v>1</v>
       </c>
       <c r="J50" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K50" s="2">
         <v>1</v>
@@ -3488,7 +3488,7 @@
         <v>1</v>
       </c>
       <c r="J51" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K51" s="2">
         <v>1</v>
@@ -3526,7 +3526,7 @@
         <v>1</v>
       </c>
       <c r="J52" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K52" s="2">
         <v>1</v>
@@ -3564,7 +3564,7 @@
         <v>1</v>
       </c>
       <c r="J53" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K53" s="2">
         <v>1</v>
@@ -3602,7 +3602,7 @@
         <v>1</v>
       </c>
       <c r="J54" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K54" s="2">
         <v>1</v>
@@ -3640,7 +3640,7 @@
         <v>1</v>
       </c>
       <c r="J55" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K55" s="2">
         <v>1</v>
@@ -3680,7 +3680,7 @@
         <v>2</v>
       </c>
       <c r="J56" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K56" s="2">
         <v>1</v>
@@ -3721,7 +3721,7 @@
         <v>2</v>
       </c>
       <c r="J57" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K57" s="2">
         <v>1</v>
@@ -3762,7 +3762,7 @@
         <v>2</v>
       </c>
       <c r="J58" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K58" s="2">
         <v>1</v>
@@ -3803,7 +3803,7 @@
         <v>2</v>
       </c>
       <c r="J59" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K59" s="2">
         <v>1</v>
@@ -3844,7 +3844,7 @@
         <v>2</v>
       </c>
       <c r="J60" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K60" s="2">
         <v>1</v>
@@ -3885,7 +3885,7 @@
         <v>2</v>
       </c>
       <c r="J61" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K61" s="2">
         <v>1</v>
@@ -3924,7 +3924,7 @@
         <v>2</v>
       </c>
       <c r="J62" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K62" s="2">
         <v>1</v>
@@ -3962,7 +3962,7 @@
         <v>2</v>
       </c>
       <c r="J63" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K63" s="2">
         <v>1</v>
@@ -4000,7 +4000,7 @@
         <v>2</v>
       </c>
       <c r="J64" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K64" s="2">
         <v>1</v>
@@ -4040,7 +4040,7 @@
         <v>3</v>
       </c>
       <c r="J65" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K65" s="2">
         <v>1</v>
@@ -4081,7 +4081,7 @@
         <v>3</v>
       </c>
       <c r="J66" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K66" s="2">
         <v>1</v>
@@ -4122,7 +4122,7 @@
         <v>3</v>
       </c>
       <c r="J67" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K67" s="2">
         <v>1</v>
@@ -4163,7 +4163,7 @@
         <v>3</v>
       </c>
       <c r="J68" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K68" s="2">
         <v>1</v>
@@ -4204,7 +4204,7 @@
         <v>3</v>
       </c>
       <c r="J69" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K69" s="2">
         <v>1</v>
@@ -4245,7 +4245,7 @@
         <v>3</v>
       </c>
       <c r="J70" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K70" s="2">
         <v>1</v>
@@ -4286,7 +4286,7 @@
         <v>4</v>
       </c>
       <c r="J71" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K71" s="2">
         <v>1</v>
@@ -4327,7 +4327,7 @@
         <v>4</v>
       </c>
       <c r="J72" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K72" s="2">
         <v>1</v>
@@ -4368,7 +4368,7 @@
         <v>4</v>
       </c>
       <c r="J73" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K73" s="2">
         <v>1</v>
@@ -4407,7 +4407,7 @@
         <v>1</v>
       </c>
       <c r="J75" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K75" s="2">
         <v>1</v>
@@ -4445,7 +4445,7 @@
         <v>1</v>
       </c>
       <c r="J76" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K76" s="2">
         <v>1</v>
@@ -4485,7 +4485,7 @@
         <v>1</v>
       </c>
       <c r="J77" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K77" s="2">
         <v>1</v>
@@ -4526,7 +4526,7 @@
         <v>1</v>
       </c>
       <c r="J78" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K78" s="2">
         <v>1</v>
@@ -4567,7 +4567,7 @@
         <v>1</v>
       </c>
       <c r="J79" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K79" s="2">
         <v>1</v>
@@ -4606,7 +4606,7 @@
         <v>1</v>
       </c>
       <c r="J80" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K80" s="2">
         <v>1</v>
@@ -4644,7 +4644,7 @@
         <v>1</v>
       </c>
       <c r="J81" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K81" s="2">
         <v>1</v>
@@ -4682,7 +4682,7 @@
         <v>1</v>
       </c>
       <c r="J82" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K82" s="2">
         <v>1</v>
@@ -4720,7 +4720,7 @@
         <v>1</v>
       </c>
       <c r="J83" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K83" s="2">
         <v>1</v>
@@ -4758,7 +4758,7 @@
         <v>1</v>
       </c>
       <c r="J84" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K84" s="2">
         <v>1</v>
@@ -4796,7 +4796,7 @@
         <v>1</v>
       </c>
       <c r="J85" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K85" s="2">
         <v>1</v>
@@ -4834,7 +4834,7 @@
         <v>1</v>
       </c>
       <c r="J86" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K86" s="2">
         <v>1</v>
@@ -4872,7 +4872,7 @@
         <v>2</v>
       </c>
       <c r="J87" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K87" s="2">
         <v>1</v>
@@ -4910,7 +4910,7 @@
         <v>2</v>
       </c>
       <c r="J88" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K88" s="2">
         <v>1</v>
@@ -4948,7 +4948,7 @@
         <v>2</v>
       </c>
       <c r="J89" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K89" s="2">
         <v>1</v>
@@ -4986,7 +4986,7 @@
         <v>2</v>
       </c>
       <c r="J90" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K90" s="2">
         <v>1</v>
@@ -5024,7 +5024,7 @@
         <v>2</v>
       </c>
       <c r="J91" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K91" s="2">
         <v>1</v>
@@ -5062,7 +5062,7 @@
         <v>2</v>
       </c>
       <c r="J92" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K92" s="2">
         <v>1</v>
@@ -5100,7 +5100,7 @@
         <v>2</v>
       </c>
       <c r="J93" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K93" s="2">
         <v>1</v>
@@ -5138,7 +5138,7 @@
         <v>2</v>
       </c>
       <c r="J94" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K94" s="2">
         <v>1</v>
@@ -5176,7 +5176,7 @@
         <v>2</v>
       </c>
       <c r="J95" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K95" s="2">
         <v>1</v>
@@ -5214,7 +5214,7 @@
         <v>3</v>
       </c>
       <c r="J96" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K96" s="2">
         <v>1</v>
@@ -5252,7 +5252,7 @@
         <v>3</v>
       </c>
       <c r="J97" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K97" s="2">
         <v>1</v>
@@ -5290,7 +5290,7 @@
         <v>3</v>
       </c>
       <c r="J98" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K98" s="2">
         <v>1</v>
@@ -5328,7 +5328,7 @@
         <v>3</v>
       </c>
       <c r="J99" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K99" s="2">
         <v>1</v>
@@ -5366,7 +5366,7 @@
         <v>3</v>
       </c>
       <c r="J100" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K100" s="2">
         <v>1</v>
@@ -5404,7 +5404,7 @@
         <v>3</v>
       </c>
       <c r="J101" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K101" s="2">
         <v>1</v>
@@ -5442,7 +5442,7 @@
         <v>4</v>
       </c>
       <c r="J102" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K102" s="2">
         <v>1</v>
@@ -5480,7 +5480,7 @@
         <v>4</v>
       </c>
       <c r="J103" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K103" s="2">
         <v>1</v>
@@ -5518,7 +5518,7 @@
         <v>4</v>
       </c>
       <c r="J104" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K104" s="2">
         <v>1</v>
@@ -5556,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="J107" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K107" s="2">
         <v>1</v>
@@ -5594,7 +5594,7 @@
         <v>1</v>
       </c>
       <c r="J108" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K108" s="2">
         <v>1</v>
@@ -5632,7 +5632,7 @@
         <v>1</v>
       </c>
       <c r="J109" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K109" s="2">
         <v>1</v>
@@ -5670,7 +5670,7 @@
         <v>1</v>
       </c>
       <c r="J110" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K110" s="2">
         <v>1</v>
@@ -5708,7 +5708,7 @@
         <v>1</v>
       </c>
       <c r="J111" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K111" s="2">
         <v>1</v>
@@ -5746,7 +5746,7 @@
         <v>1</v>
       </c>
       <c r="J112" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K112" s="2">
         <v>1</v>
@@ -5784,7 +5784,7 @@
         <v>1</v>
       </c>
       <c r="J113" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K113" s="2">
         <v>1</v>
@@ -5822,7 +5822,7 @@
         <v>1</v>
       </c>
       <c r="J114" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K114" s="2">
         <v>1</v>
@@ -5860,7 +5860,7 @@
         <v>1</v>
       </c>
       <c r="J115" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K115" s="2">
         <v>1</v>
@@ -5898,7 +5898,7 @@
         <v>1</v>
       </c>
       <c r="J116" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K116" s="2">
         <v>1</v>
@@ -5936,7 +5936,7 @@
         <v>1</v>
       </c>
       <c r="J117" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K117" s="2">
         <v>1</v>
@@ -5974,7 +5974,7 @@
         <v>1</v>
       </c>
       <c r="J118" s="1">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K118" s="2">
         <v>1</v>
@@ -6012,7 +6012,7 @@
         <v>2</v>
       </c>
       <c r="J119" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K119" s="2">
         <v>1</v>
@@ -6050,7 +6050,7 @@
         <v>2</v>
       </c>
       <c r="J120" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K120" s="2">
         <v>1</v>
@@ -6088,7 +6088,7 @@
         <v>2</v>
       </c>
       <c r="J121" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K121" s="2">
         <v>1</v>
@@ -6126,7 +6126,7 @@
         <v>2</v>
       </c>
       <c r="J122" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K122" s="2">
         <v>1</v>
@@ -6164,7 +6164,7 @@
         <v>2</v>
       </c>
       <c r="J123" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K123" s="2">
         <v>1</v>
@@ -6202,7 +6202,7 @@
         <v>2</v>
       </c>
       <c r="J124" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K124" s="2">
         <v>1</v>
@@ -6240,7 +6240,7 @@
         <v>2</v>
       </c>
       <c r="J125" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K125" s="2">
         <v>1</v>
@@ -6278,7 +6278,7 @@
         <v>2</v>
       </c>
       <c r="J126" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K126" s="2">
         <v>1</v>
@@ -6316,7 +6316,7 @@
         <v>2</v>
       </c>
       <c r="J127" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="K127" s="2">
         <v>1</v>
@@ -6354,7 +6354,7 @@
         <v>3</v>
       </c>
       <c r="J128" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K128" s="2">
         <v>1</v>
@@ -6392,7 +6392,7 @@
         <v>3</v>
       </c>
       <c r="J129" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K129" s="2">
         <v>1</v>
@@ -6430,7 +6430,7 @@
         <v>3</v>
       </c>
       <c r="J130" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K130" s="2">
         <v>1</v>
@@ -6468,7 +6468,7 @@
         <v>3</v>
       </c>
       <c r="J131" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K131" s="2">
         <v>1</v>
@@ -6506,7 +6506,7 @@
         <v>3</v>
       </c>
       <c r="J132" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K132" s="2">
         <v>1</v>
@@ -6544,7 +6544,7 @@
         <v>3</v>
       </c>
       <c r="J133" s="1">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K133" s="2">
         <v>1</v>
@@ -6582,7 +6582,7 @@
         <v>4</v>
       </c>
       <c r="J134" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K134" s="2">
         <v>1</v>
@@ -6620,7 +6620,7 @@
         <v>4</v>
       </c>
       <c r="J135" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K135" s="2">
         <v>1</v>
@@ -6658,7 +6658,7 @@
         <v>4</v>
       </c>
       <c r="J136" s="1">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="K136" s="2">
         <v>1</v>
